--- a/potpourri/results/results.xlsx
+++ b/potpourri/results/results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
   <si>
     <t>Conventional generation (MW)</t>
   </si>
@@ -40,12 +40,18 @@
     <t>angle(degs)</t>
   </si>
   <si>
+    <t>Voltage(p.u.)</t>
+  </si>
+  <si>
     <t>busname</t>
   </si>
   <si>
     <t>PD(MW)</t>
   </si>
   <si>
+    <t>QD(MVar)</t>
+  </si>
+  <si>
     <t>alpha</t>
   </si>
   <si>
@@ -112,6 +118,15 @@
     <t>PGUB(MW)</t>
   </si>
   <si>
+    <t>QGLB(MVar)</t>
+  </si>
+  <si>
+    <t>qG(MVar)</t>
+  </si>
+  <si>
+    <t>QGUB(MVar)</t>
+  </si>
+  <si>
     <t>G1</t>
   </si>
   <si>
@@ -217,10 +232,13 @@
     <t>to_busname</t>
   </si>
   <si>
-    <t>pL(MW)</t>
-  </si>
-  <si>
-    <t>SLmax(MW)</t>
+    <t>pLto(MW)</t>
+  </si>
+  <si>
+    <t>pLfrom(MW)</t>
+  </si>
+  <si>
+    <t>loss(MW)</t>
   </si>
   <si>
     <t>L1-12</t>
@@ -322,7 +340,10 @@
     <t>L33-2122</t>
   </si>
   <si>
-    <t>pLT(MW)</t>
+    <t>pLTto(MW)</t>
+  </si>
+  <si>
+    <t>pLTfrom(MW)</t>
   </si>
   <si>
     <t>T1-324</t>
@@ -714,7 +735,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>2850.000000001932</v>
+        <v>1035.999966608644</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -723,7 +744,7 @@
         <v>2850</v>
       </c>
       <c r="D2">
-        <v>61001.240312277</v>
+        <v>71164.91778268501</v>
       </c>
     </row>
   </sheetData>
@@ -733,207 +754,282 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-7.014224342988088</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>-8.8766323781621</v>
+      </c>
+      <c r="C2">
+        <v>1.001413839402157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-7.103140615842057</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>-8.951800829564231</v>
+      </c>
+      <c r="C3">
+        <v>1.001475011255603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-6.404042755248816</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>-5.487371811639138</v>
+      </c>
+      <c r="C4">
+        <v>1.004517028842937</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-10.23923741441823</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>-9.03202637144938</v>
+      </c>
+      <c r="C5">
+        <v>0.9955034258093148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-10.39735554405377</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>-9.907449876801424</v>
+      </c>
+      <c r="C6">
+        <v>1.008260639452845</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-13.14961174381005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>-10.81448999019221</v>
+      </c>
+      <c r="C7">
+        <v>1.02108918284511</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-13.65044909572965</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>-12.58769810735618</v>
+      </c>
+      <c r="C8">
+        <v>1.005137416644855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-15.27656980364107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>-12.41642201878874</v>
+      </c>
+      <c r="C9">
+        <v>0.9957319463857712</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-8.409271344827609</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>-6.708215458150161</v>
+      </c>
+      <c r="C10">
+        <v>1.008275135462243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-10.34058325151292</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>-8.860194665532488</v>
+      </c>
+      <c r="C11">
+        <v>1.031492285646338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-2.790266486441518</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>-2.965646368623914</v>
+      </c>
+      <c r="C12">
+        <v>0.9874233156367803</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-2.059230817016788</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>-2.766778085211983</v>
+      </c>
+      <c r="C13">
+        <v>0.9915776847629607</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1.717228750155294E-32</v>
+      </c>
+      <c r="C14">
+        <v>1.000879236114013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.320573618039091</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>-0.6665560249641195</v>
+      </c>
+      <c r="C15">
+        <v>0.9782038935085714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>10.28199941171252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>2.861265928563993</v>
+      </c>
+      <c r="C16">
+        <v>0.9865755010586286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>9.470095193845705</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>2.523351346686917</v>
+      </c>
+      <c r="C17">
+        <v>0.9848875870736138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>14.22823337907613</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>3.915959082307656</v>
+      </c>
+      <c r="C18">
+        <v>0.9918159198704417</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>15.71124264845208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>4.461299950074305</v>
+      </c>
+      <c r="C19">
+        <v>0.991871097192813</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>8.25373724831327</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>2.428552765779183</v>
+      </c>
+      <c r="C20">
+        <v>0.9854249485856689</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>9.264510869746807</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>2.858991087720517</v>
+      </c>
+      <c r="C21">
+        <v>0.98673960100978</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>16.54779429233833</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>4.538313520596536</v>
+      </c>
+      <c r="C22">
+        <v>0.9932270240698891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>22.7285910664785</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>5.642315580810013</v>
+      </c>
+      <c r="C23">
+        <v>1.00542993921545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>10.60789879193114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>3.354995304291808</v>
+      </c>
+      <c r="C24">
+        <v>0.9876208047137668</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3.904933222719194</v>
+        <v>-0.3079678329274433</v>
+      </c>
+      <c r="C25">
+        <v>0.9780814001805032</v>
       </c>
     </row>
   </sheetData>
@@ -943,26 +1039,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -971,12 +1070,15 @@
         <v>108</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>22</v>
+      </c>
+      <c r="E2">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -985,12 +1087,15 @@
         <v>195</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>13</v>
@@ -999,12 +1104,15 @@
         <v>265</v>
       </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>54</v>
+      </c>
+      <c r="E4">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>14</v>
@@ -1013,12 +1121,15 @@
         <v>194</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>15</v>
@@ -1027,12 +1138,15 @@
         <v>317</v>
       </c>
       <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>16</v>
@@ -1041,12 +1155,15 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>0.367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>18</v>
@@ -1055,12 +1172,15 @@
         <v>333</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>68</v>
+      </c>
+      <c r="E8">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>19</v>
@@ -1069,12 +1189,15 @@
         <v>181</v>
       </c>
       <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -1083,12 +1206,15 @@
         <v>97</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>0.572</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -1097,12 +1223,15 @@
         <v>128</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>26</v>
+      </c>
+      <c r="E11">
+        <v>0.318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -1111,12 +1240,15 @@
         <v>180</v>
       </c>
       <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>0.329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -1125,12 +1257,15 @@
         <v>74</v>
       </c>
       <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>0.5639999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -1139,12 +1274,15 @@
         <v>71</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1153,12 +1291,15 @@
         <v>136</v>
       </c>
       <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>0.541</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -1167,12 +1308,15 @@
         <v>125</v>
       </c>
       <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>25</v>
+      </c>
+      <c r="E16">
+        <v>0.607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -1181,12 +1325,15 @@
         <v>171</v>
       </c>
       <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="E17">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>9</v>
@@ -1195,7 +1342,10 @@
         <v>175</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>0.412</v>
       </c>
     </row>
   </sheetData>
@@ -1205,32 +1355,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1244,10 +1403,19 @@
       <c r="F2">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3.994</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -1256,15 +1424,24 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>57.074</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="I3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -1273,15 +1450,24 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>57.074</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="I4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>13</v>
@@ -1290,15 +1476,24 @@
         <v>69</v>
       </c>
       <c r="E5">
-        <v>76.259</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>197</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>14.796</v>
+      </c>
+      <c r="I5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>13</v>
@@ -1307,15 +1502,24 @@
         <v>69</v>
       </c>
       <c r="E6">
-        <v>76.259</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>197</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>14.796</v>
+      </c>
+      <c r="I6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -1324,15 +1528,24 @@
         <v>69</v>
       </c>
       <c r="E7">
-        <v>76.259</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>197</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>14.796</v>
+      </c>
+      <c r="I7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>14</v>
@@ -1341,15 +1554,24 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>-50</v>
+      </c>
+      <c r="H8">
+        <v>-24.864</v>
+      </c>
+      <c r="I8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>15</v>
@@ -1363,10 +1585,19 @@
       <c r="F9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>2.891</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -1380,10 +1611,19 @@
       <c r="F10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>2.891</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>15</v>
@@ -1397,10 +1637,19 @@
       <c r="F11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>2.891</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>15</v>
@@ -1414,10 +1663,19 @@
       <c r="F12">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2.891</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1431,10 +1689,19 @@
       <c r="F13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>3.994</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>15</v>
@@ -1448,10 +1715,19 @@
       <c r="F14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2.891</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>15</v>
@@ -1460,15 +1736,24 @@
         <v>54.29999999999999</v>
       </c>
       <c r="E15">
-        <v>155</v>
+        <v>54.3</v>
       </c>
       <c r="F15">
         <v>155</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15">
+        <v>-50</v>
+      </c>
+      <c r="H15">
+        <v>-20.821</v>
+      </c>
+      <c r="I15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>16</v>
@@ -1477,15 +1762,24 @@
         <v>54.29999999999999</v>
       </c>
       <c r="E16">
-        <v>155</v>
+        <v>54.3</v>
       </c>
       <c r="F16">
         <v>155</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>-50</v>
+      </c>
+      <c r="H16">
+        <v>-22.079</v>
+      </c>
+      <c r="I16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>18</v>
@@ -1494,15 +1788,24 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>-50</v>
+      </c>
+      <c r="H17">
+        <v>-13.457</v>
+      </c>
+      <c r="I17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>21</v>
@@ -1511,15 +1814,24 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>400</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>-50</v>
+      </c>
+      <c r="H18">
+        <v>-13.931</v>
+      </c>
+      <c r="I18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>22</v>
@@ -1528,15 +1840,24 @@
         <v>10</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F19">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>-10</v>
+      </c>
+      <c r="H19">
+        <v>0.954</v>
+      </c>
+      <c r="I19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -1545,15 +1866,24 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>-10</v>
+      </c>
+      <c r="H20">
+        <v>0.954</v>
+      </c>
+      <c r="I20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>22</v>
@@ -1562,15 +1892,24 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>-10</v>
+      </c>
+      <c r="H21">
+        <v>0.954</v>
+      </c>
+      <c r="I21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>22</v>
@@ -1579,15 +1918,24 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22">
+        <v>-10</v>
+      </c>
+      <c r="H22">
+        <v>0.954</v>
+      </c>
+      <c r="I22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1596,15 +1944,24 @@
         <v>10</v>
       </c>
       <c r="E23">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23">
+        <v>-10</v>
+      </c>
+      <c r="H23">
+        <v>0.954</v>
+      </c>
+      <c r="I23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1613,15 +1970,24 @@
         <v>15.2</v>
       </c>
       <c r="E24">
-        <v>76</v>
+        <v>15.2</v>
       </c>
       <c r="F24">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24">
+        <v>-25</v>
+      </c>
+      <c r="H24">
+        <v>-15.55</v>
+      </c>
+      <c r="I24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>22</v>
@@ -1630,15 +1996,24 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25">
+        <v>-10</v>
+      </c>
+      <c r="H25">
+        <v>0.954</v>
+      </c>
+      <c r="I25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B26">
         <v>23</v>
@@ -1647,15 +2022,24 @@
         <v>54.29999999999999</v>
       </c>
       <c r="E26">
-        <v>155</v>
+        <v>54.3</v>
       </c>
       <c r="F26">
         <v>155</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26">
+        <v>-50</v>
+      </c>
+      <c r="H26">
+        <v>-28.2</v>
+      </c>
+      <c r="I26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B27">
         <v>23</v>
@@ -1664,15 +2048,24 @@
         <v>54.29999999999999</v>
       </c>
       <c r="E27">
-        <v>155</v>
+        <v>54.3</v>
       </c>
       <c r="F27">
         <v>155</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27">
+        <v>-50</v>
+      </c>
+      <c r="H27">
+        <v>-28.2</v>
+      </c>
+      <c r="I27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>23</v>
@@ -1681,15 +2074,24 @@
         <v>140</v>
       </c>
       <c r="E28">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="F28">
         <v>350</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28">
+        <v>-25</v>
+      </c>
+      <c r="H28">
+        <v>-1.859</v>
+      </c>
+      <c r="I28">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1698,15 +2100,24 @@
         <v>15.2</v>
       </c>
       <c r="E29">
-        <v>76</v>
+        <v>15.2</v>
       </c>
       <c r="F29">
         <v>76</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29">
+        <v>-25</v>
+      </c>
+      <c r="H29">
+        <v>-15.55</v>
+      </c>
+      <c r="I29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -1720,10 +2131,19 @@
       <c r="F30">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>3.987</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -1737,10 +2157,19 @@
       <c r="F31">
         <v>20</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>3.987</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -1749,15 +2178,24 @@
         <v>15.2</v>
       </c>
       <c r="E32">
-        <v>76</v>
+        <v>15.2</v>
       </c>
       <c r="F32">
         <v>76</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32">
+        <v>-25</v>
+      </c>
+      <c r="H32">
+        <v>-15.606</v>
+      </c>
+      <c r="I32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1766,15 +2204,24 @@
         <v>15.2</v>
       </c>
       <c r="E33">
-        <v>76</v>
+        <v>15.2</v>
       </c>
       <c r="F33">
         <v>76</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33">
+        <v>-25</v>
+      </c>
+      <c r="H33">
+        <v>-15.606</v>
+      </c>
+      <c r="I33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -1783,10 +2230,19 @@
         <v>25</v>
       </c>
       <c r="E34">
-        <v>57.074</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>100</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="I34">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1796,27 +2252,36 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1826,29 +2291,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>71</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1857,15 +2325,18 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>11.1646166899527</v>
+        <v>-9.06491579742398</v>
       </c>
       <c r="E2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>9.067164999838626</v>
+      </c>
+      <c r="F2">
+        <v>0.002249202414647544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1874,15 +2345,18 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>-5.042461051655756</v>
+        <v>26.95377887122049</v>
       </c>
       <c r="E3">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>-26.54891993851434</v>
+      </c>
+      <c r="F3">
+        <v>0.404858932706148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1891,15 +2365,18 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>69.87784436159346</v>
+        <v>-18.13199324868041</v>
       </c>
       <c r="E4">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>18.23896436268143</v>
+      </c>
+      <c r="F4">
+        <v>0.1069711140010116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1908,15 +2385,18 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>43.20064309108731</v>
+        <v>-2.170757884892138</v>
       </c>
       <c r="E5">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>2.177960719701232</v>
+      </c>
+      <c r="F5">
+        <v>0.007202834809093631</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1925,15 +2405,18 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>54.96397359886296</v>
+        <v>-13.62585884460771</v>
       </c>
       <c r="E6">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>13.81101796380883</v>
+      </c>
+      <c r="F6">
+        <v>0.1851591192011171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -1942,15 +2425,18 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>29.40995054023201</v>
+        <v>-16.17622179390136</v>
       </c>
       <c r="E7">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>16.27283349831609</v>
+      </c>
+      <c r="F7">
+        <v>0.09661170441473133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1959,15 +2445,18 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-30.79935690849553</v>
+        <v>39.99061092126085</v>
       </c>
       <c r="E8">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>-39.56683373373679</v>
+      </c>
+      <c r="F8">
+        <v>0.4237771875240715</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1976,15 +2465,18 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1.12215563852347</v>
+        <v>26.79852487197217</v>
       </c>
       <c r="E9">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>-26.55531476502497</v>
+      </c>
+      <c r="F9">
+        <v>0.2432101069471948</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1993,15 +2485,18 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-81.03602640122735</v>
+        <v>60.48371497749191</v>
       </c>
       <c r="E10">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>-60.00271306305106</v>
+      </c>
+      <c r="F10">
+        <v>0.4810019144408484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -2010,15 +2505,18 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>46.22338825393371</v>
+        <v>0.8666325320490833</v>
       </c>
       <c r="E11">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>-0.828132592992624</v>
+      </c>
+      <c r="F11">
+        <v>0.03849993905645933</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -2027,15 +2525,18 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-72.59658923284501</v>
+        <v>59.27879633480803</v>
       </c>
       <c r="E12">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>-57.79375249211599</v>
+      </c>
+      <c r="F12">
+        <v>1.485043842692035</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -2044,15 +2545,18 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-52.18002251289347</v>
+        <v>41.8748633345406</v>
       </c>
       <c r="E13">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>-41.1063102571603</v>
+      </c>
+      <c r="F13">
+        <v>0.7685530773803018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B14">
         <v>11</v>
@@ -2061,15 +2565,18 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>-102.3095319253323</v>
+        <v>109.6011981598082</v>
       </c>
       <c r="E14">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>-108.8520696999671</v>
+      </c>
+      <c r="F14">
+        <v>0.7491284598411196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B15">
         <v>11</v>
@@ -2078,15 +2585,18 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>-171.645202981374</v>
+        <v>88.67183392873311</v>
       </c>
       <c r="E15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>-88.17328637669706</v>
+      </c>
+      <c r="F15">
+        <v>0.4985475520360438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B16">
         <v>12</v>
@@ -2095,15 +2605,18 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>-75.50495339385677</v>
+        <v>101.7894053193537</v>
       </c>
       <c r="E16">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>-101.1536177450771</v>
+      </c>
+      <c r="F16">
+        <v>0.635787574276625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B17">
         <v>12</v>
@@ -2112,15 +2625,18 @@
         <v>23</v>
       </c>
       <c r="D17">
-        <v>-228.864511855415</v>
+        <v>106.5771639652878</v>
       </c>
       <c r="E17">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>-105.1150167894688</v>
+      </c>
+      <c r="F17">
+        <v>1.462147175819006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B18">
         <v>13</v>
@@ -2129,15 +2645,18 @@
         <v>23</v>
       </c>
       <c r="D18">
-        <v>-214.0378735693957</v>
+        <v>64.12976855615607</v>
       </c>
       <c r="E18">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>-63.60959296241284</v>
+      </c>
+      <c r="F18">
+        <v>0.5201755937432218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B19">
         <v>14</v>
@@ -2146,15 +2665,18 @@
         <v>16</v>
       </c>
       <c r="D19">
-        <v>-365.6452029821529</v>
+        <v>138.2004012579186</v>
       </c>
       <c r="E19">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>-137.2154395946111</v>
+      </c>
+      <c r="F19">
+        <v>0.984961663307482</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B20">
         <v>15</v>
@@ -2163,15 +2685,18 @@
         <v>16</v>
       </c>
       <c r="D20">
-        <v>81.90983706708232</v>
+        <v>-33.78791740353954</v>
       </c>
       <c r="E20">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>33.81442658588467</v>
+      </c>
+      <c r="F20">
+        <v>0.02650918234513022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B21">
         <v>15</v>
@@ -2180,15 +2705,18 @@
         <v>21</v>
       </c>
       <c r="D21">
-        <v>-223.1811243296438</v>
+        <v>59.3871837666554</v>
       </c>
       <c r="E21">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>-59.15908243433773</v>
+      </c>
+      <c r="F21">
+        <v>0.2281013323176651</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B22">
         <v>15</v>
@@ -2197,15 +2725,18 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>-223.1811243296438</v>
+        <v>59.3871837666554</v>
       </c>
       <c r="E22">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>-59.15908243433773</v>
+      </c>
+      <c r="F22">
+        <v>0.2281013323176651</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -2214,15 +2745,18 @@
         <v>24</v>
       </c>
       <c r="D23">
-        <v>214.4524115906367</v>
+        <v>-102.7759528167307</v>
       </c>
       <c r="E23">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>103.5157424969224</v>
+      </c>
+      <c r="F23">
+        <v>0.7397896801916826</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B24">
         <v>16</v>
@@ -2231,15 +2765,18 @@
         <v>17</v>
       </c>
       <c r="D24">
-        <v>-320.637751340304</v>
+        <v>93.66218532542231</v>
       </c>
       <c r="E24">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>-93.35961086188355</v>
+      </c>
+      <c r="F24">
+        <v>0.3025744635387628</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B25">
         <v>16</v>
@@ -2248,15 +2785,18 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>91.90238542136298</v>
+        <v>-6.54267629861722</v>
       </c>
       <c r="E25">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>6.544304880753604</v>
+      </c>
+      <c r="F25">
+        <v>0.001628582136384282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B26">
         <v>17</v>
@@ -2265,15 +2805,18 @@
         <v>18</v>
       </c>
       <c r="D26">
-        <v>-179.7457957469697</v>
+        <v>64.10686999533122</v>
       </c>
       <c r="E26">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>-64.03069668473964</v>
+      </c>
+      <c r="F26">
+        <v>0.07617331059158738</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B27">
         <v>17</v>
@@ -2282,15 +2825,18 @@
         <v>22</v>
       </c>
       <c r="D27">
-        <v>-140.8919555958046</v>
+        <v>29.76212273692076</v>
       </c>
       <c r="E27">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>-29.63148864068269</v>
+      </c>
+      <c r="F27">
+        <v>0.1306340962380748</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B28">
         <v>18</v>
@@ -2299,15 +2845,18 @@
         <v>21</v>
       </c>
       <c r="D28">
-        <v>-56.3728978717607</v>
+        <v>5.683372288646154</v>
       </c>
       <c r="E28">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>-5.68162066644945</v>
+      </c>
+      <c r="F28">
+        <v>0.001751622196704411</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B29">
         <v>18</v>
@@ -2316,15 +2865,18 @@
         <v>21</v>
       </c>
       <c r="D29">
-        <v>-56.3728978717607</v>
+        <v>5.683372288646154</v>
       </c>
       <c r="E29">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>-5.68162066644945</v>
+      </c>
+      <c r="F29">
+        <v>0.001751622196704411</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B30">
         <v>19</v>
@@ -2333,15 +2885,18 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>-44.54880728787725</v>
+        <v>18.56936008705726</v>
       </c>
       <c r="E30">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>-18.55125074332018</v>
+      </c>
+      <c r="F30">
+        <v>0.0181093437370744</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B31">
         <v>19</v>
@@ -2350,15 +2905,18 @@
         <v>20</v>
       </c>
       <c r="D31">
-        <v>-44.54880728761061</v>
+        <v>18.56936008705726</v>
       </c>
       <c r="E31">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>-18.55125074332018</v>
+      </c>
+      <c r="F31">
+        <v>0.0181093437370744</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B32">
         <v>20</v>
@@ -2367,15 +2925,18 @@
         <v>23</v>
       </c>
       <c r="D32">
-        <v>-108.5488072853795</v>
+        <v>38.94653203930537</v>
       </c>
       <c r="E32">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>-38.90296859826503</v>
+      </c>
+      <c r="F32">
+        <v>0.04356344104034515</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -2384,15 +2945,18 @@
         <v>23</v>
       </c>
       <c r="D33">
-        <v>-108.5488072853795</v>
+        <v>38.94653203930537</v>
       </c>
       <c r="E33">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>-38.90296859826503</v>
+      </c>
+      <c r="F33">
+        <v>0.04356344104034515</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B34">
         <v>21</v>
@@ -2401,10 +2965,13 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>-159.108044402809</v>
+        <v>30.23787126379522</v>
       </c>
       <c r="E34">
-        <v>500</v>
+        <v>-30.14111311059066</v>
+      </c>
+      <c r="F34">
+        <v>0.09675815320456804</v>
       </c>
     </row>
   </sheetData>
@@ -2414,29 +2981,32 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -2445,15 +3015,18 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>-214.4524115906367</v>
+        <v>102.7759528167307</v>
       </c>
       <c r="E2">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>-102.521366472144</v>
+      </c>
+      <c r="F2">
+        <v>0.2545863445867047</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -2462,15 +3035,18 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>-116.88931521382</v>
+        <v>75.48600449002028</v>
       </c>
       <c r="E3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>-75.34903148264421</v>
+      </c>
+      <c r="F3">
+        <v>0.1369730073760622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -2479,15 +3055,18 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>-132.0966803878003</v>
+        <v>79.949018079864</v>
       </c>
       <c r="E4">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>-79.79386416896489</v>
+      </c>
+      <c r="F4">
+        <v>0.1551539108991196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -2496,15 +3075,18 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>-157.065419688943</v>
+        <v>121.5393515866439</v>
       </c>
       <c r="E5">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>-121.1760275501905</v>
+      </c>
+      <c r="F5">
+        <v>0.3633240364533386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B6">
         <v>10</v>
@@ -2513,10 +3095,13 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>-172.2727848631612</v>
+        <v>126.3196164546818</v>
       </c>
       <c r="E6">
-        <v>400</v>
+        <v>-125.9370141518932</v>
+      </c>
+      <c r="F6">
+        <v>0.3826023027886594</v>
       </c>
     </row>
   </sheetData>

--- a/potpourri/results/results.xlsx
+++ b/potpourri/results/results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="336">
   <si>
     <t>Conventional generation (MW)</t>
   </si>
@@ -55,55 +55,271 @@
     <t>alpha</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>D13</t>
-  </si>
-  <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>D16</t>
-  </si>
-  <si>
-    <t>D18</t>
-  </si>
-  <si>
-    <t>D19</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>D9</t>
+    <t>D1037</t>
+  </si>
+  <si>
+    <t>D1163</t>
+  </si>
+  <si>
+    <t>D1317</t>
+  </si>
+  <si>
+    <t>D1367</t>
+  </si>
+  <si>
+    <t>D1445</t>
+  </si>
+  <si>
+    <t>D1531</t>
+  </si>
+  <si>
+    <t>D1579</t>
+  </si>
+  <si>
+    <t>D1611</t>
+  </si>
+  <si>
+    <t>D1616</t>
+  </si>
+  <si>
+    <t>D1676</t>
+  </si>
+  <si>
+    <t>D1815</t>
+  </si>
+  <si>
+    <t>D1968</t>
+  </si>
+  <si>
+    <t>D2107</t>
+  </si>
+  <si>
+    <t>D2154</t>
+  </si>
+  <si>
+    <t>D2168</t>
+  </si>
+  <si>
+    <t>D2267</t>
+  </si>
+  <si>
+    <t>D2268</t>
+  </si>
+  <si>
+    <t>D228</t>
+  </si>
+  <si>
+    <t>D2299</t>
+  </si>
+  <si>
+    <t>D2441</t>
+  </si>
+  <si>
+    <t>D2449</t>
+  </si>
+  <si>
+    <t>D2520</t>
+  </si>
+  <si>
+    <t>D271</t>
+  </si>
+  <si>
+    <t>D2870</t>
+  </si>
+  <si>
+    <t>D2908</t>
+  </si>
+  <si>
+    <t>D3097</t>
+  </si>
+  <si>
+    <t>D317</t>
+  </si>
+  <si>
+    <t>D3242</t>
+  </si>
+  <si>
+    <t>D3279</t>
+  </si>
+  <si>
+    <t>D3493</t>
+  </si>
+  <si>
+    <t>D3506</t>
+  </si>
+  <si>
+    <t>D3659</t>
+  </si>
+  <si>
+    <t>D4014</t>
+  </si>
+  <si>
+    <t>D4423</t>
+  </si>
+  <si>
+    <t>D4427</t>
+  </si>
+  <si>
+    <t>D4495</t>
+  </si>
+  <si>
+    <t>D4586</t>
+  </si>
+  <si>
+    <t>D4665</t>
+  </si>
+  <si>
+    <t>D4929</t>
+  </si>
+  <si>
+    <t>D5097</t>
+  </si>
+  <si>
+    <t>D5155</t>
+  </si>
+  <si>
+    <t>D5210</t>
+  </si>
+  <si>
+    <t>D5416</t>
+  </si>
+  <si>
+    <t>D5509</t>
+  </si>
+  <si>
+    <t>D5587</t>
+  </si>
+  <si>
+    <t>D5762</t>
+  </si>
+  <si>
+    <t>D5776</t>
+  </si>
+  <si>
+    <t>D5848</t>
+  </si>
+  <si>
+    <t>D5996</t>
+  </si>
+  <si>
+    <t>D6069</t>
+  </si>
+  <si>
+    <t>D6233</t>
+  </si>
+  <si>
+    <t>D6293</t>
+  </si>
+  <si>
+    <t>D6542</t>
+  </si>
+  <si>
+    <t>D659</t>
+  </si>
+  <si>
+    <t>D6704</t>
+  </si>
+  <si>
+    <t>D6798</t>
+  </si>
+  <si>
+    <t>D6826</t>
+  </si>
+  <si>
+    <t>D6833</t>
+  </si>
+  <si>
+    <t>D7051</t>
+  </si>
+  <si>
+    <t>D7180</t>
+  </si>
+  <si>
+    <t>D7279</t>
+  </si>
+  <si>
+    <t>D7526</t>
+  </si>
+  <si>
+    <t>D7563</t>
+  </si>
+  <si>
+    <t>D7637</t>
+  </si>
+  <si>
+    <t>D7762</t>
+  </si>
+  <si>
+    <t>D7829</t>
+  </si>
+  <si>
+    <t>D792</t>
+  </si>
+  <si>
+    <t>D7960</t>
+  </si>
+  <si>
+    <t>D8103</t>
+  </si>
+  <si>
+    <t>D8179</t>
+  </si>
+  <si>
+    <t>D8181</t>
+  </si>
+  <si>
+    <t>D8229</t>
+  </si>
+  <si>
+    <t>D8329</t>
+  </si>
+  <si>
+    <t>D8335</t>
+  </si>
+  <si>
+    <t>D8420</t>
+  </si>
+  <si>
+    <t>D8574</t>
+  </si>
+  <si>
+    <t>D8581</t>
+  </si>
+  <si>
+    <t>D8605</t>
+  </si>
+  <si>
+    <t>D8847</t>
+  </si>
+  <si>
+    <t>D89</t>
+  </si>
+  <si>
+    <t>D8921</t>
+  </si>
+  <si>
+    <t>D8964</t>
+  </si>
+  <si>
+    <t>D9024</t>
+  </si>
+  <si>
+    <t>D9025</t>
+  </si>
+  <si>
+    <t>D9064</t>
+  </si>
+  <si>
+    <t>D913</t>
+  </si>
+  <si>
+    <t>D9192</t>
+  </si>
+  <si>
+    <t>D9239</t>
+  </si>
+  <si>
+    <t>D955</t>
   </si>
   <si>
     <t>PGLB(MW)</t>
@@ -139,75 +355,12 @@
     <t>G12</t>
   </si>
   <si>
-    <t>G13</t>
-  </si>
-  <si>
-    <t>G14</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>G16</t>
-  </si>
-  <si>
-    <t>G17</t>
-  </si>
-  <si>
-    <t>G18</t>
-  </si>
-  <si>
-    <t>G19</t>
-  </si>
-  <si>
     <t>G2</t>
   </si>
   <si>
-    <t>G20</t>
-  </si>
-  <si>
-    <t>G21</t>
-  </si>
-  <si>
-    <t>G22</t>
-  </si>
-  <si>
-    <t>G23</t>
-  </si>
-  <si>
-    <t>G24</t>
-  </si>
-  <si>
-    <t>G25</t>
-  </si>
-  <si>
-    <t>G26</t>
-  </si>
-  <si>
-    <t>G27</t>
-  </si>
-  <si>
-    <t>G28</t>
-  </si>
-  <si>
-    <t>G29</t>
-  </si>
-  <si>
     <t>G3</t>
   </si>
   <si>
-    <t>G30</t>
-  </si>
-  <si>
-    <t>G31</t>
-  </si>
-  <si>
-    <t>G32</t>
-  </si>
-  <si>
-    <t>G33</t>
-  </si>
-  <si>
     <t>G4</t>
   </si>
   <si>
@@ -241,103 +394,538 @@
     <t>loss(MW)</t>
   </si>
   <si>
-    <t>L1-12</t>
-  </si>
-  <si>
-    <t>L2-13</t>
-  </si>
-  <si>
-    <t>L3-15</t>
-  </si>
-  <si>
-    <t>L4-24</t>
-  </si>
-  <si>
-    <t>L5-26</t>
-  </si>
-  <si>
-    <t>L6-39</t>
-  </si>
-  <si>
-    <t>L7-49</t>
-  </si>
-  <si>
-    <t>L8-510</t>
-  </si>
-  <si>
-    <t>L9-610</t>
-  </si>
-  <si>
-    <t>L10-78</t>
-  </si>
-  <si>
-    <t>L11-89</t>
-  </si>
-  <si>
-    <t>L12-810</t>
-  </si>
-  <si>
-    <t>L13-1113</t>
-  </si>
-  <si>
-    <t>L14-1114</t>
-  </si>
-  <si>
-    <t>L15-1213</t>
-  </si>
-  <si>
-    <t>L16-1223</t>
-  </si>
-  <si>
-    <t>L17-1323</t>
-  </si>
-  <si>
-    <t>L18-1416</t>
-  </si>
-  <si>
-    <t>L19-1516</t>
-  </si>
-  <si>
-    <t>L20-1521</t>
-  </si>
-  <si>
-    <t>L21-1521</t>
-  </si>
-  <si>
-    <t>L22-1524</t>
-  </si>
-  <si>
-    <t>L23-1617</t>
-  </si>
-  <si>
-    <t>L24-1619</t>
-  </si>
-  <si>
-    <t>L25-1718</t>
-  </si>
-  <si>
-    <t>L26-1722</t>
-  </si>
-  <si>
-    <t>L27-1821</t>
-  </si>
-  <si>
-    <t>L28-1821</t>
-  </si>
-  <si>
-    <t>L29-1920</t>
-  </si>
-  <si>
-    <t>L30-1920</t>
-  </si>
-  <si>
-    <t>L31-2023</t>
-  </si>
-  <si>
-    <t>L32-2023</t>
-  </si>
-  <si>
-    <t>L33-2122</t>
+    <t>L1-3097659</t>
+  </si>
+  <si>
+    <t>L2-90244929</t>
+  </si>
+  <si>
+    <t>L3-18156542</t>
+  </si>
+  <si>
+    <t>L4-65421445</t>
+  </si>
+  <si>
+    <t>L5-60696833</t>
+  </si>
+  <si>
+    <t>L6-60692268</t>
+  </si>
+  <si>
+    <t>L7-60697180</t>
+  </si>
+  <si>
+    <t>L8-60696293</t>
+  </si>
+  <si>
+    <t>L9-19689192</t>
+  </si>
+  <si>
+    <t>L10-19683493</t>
+  </si>
+  <si>
+    <t>L11-1968955</t>
+  </si>
+  <si>
+    <t>L12-1968228</t>
+  </si>
+  <si>
+    <t>L13-19686826</t>
+  </si>
+  <si>
+    <t>L14-19688964</t>
+  </si>
+  <si>
+    <t>L15-19685776</t>
+  </si>
+  <si>
+    <t>L16-9192955</t>
+  </si>
+  <si>
+    <t>L17-91926826</t>
+  </si>
+  <si>
+    <t>L18-91928964</t>
+  </si>
+  <si>
+    <t>L19-85741616</t>
+  </si>
+  <si>
+    <t>L20-85741163</t>
+  </si>
+  <si>
+    <t>L21-85749064</t>
+  </si>
+  <si>
+    <t>L22-85748921</t>
+  </si>
+  <si>
+    <t>L23-34932299</t>
+  </si>
+  <si>
+    <t>L24-22994423</t>
+  </si>
+  <si>
+    <t>L25-68262299</t>
+  </si>
+  <si>
+    <t>L26-75632299</t>
+  </si>
+  <si>
+    <t>L27-44272299</t>
+  </si>
+  <si>
+    <t>L28-83352299</t>
+  </si>
+  <si>
+    <t>L29-51552299</t>
+  </si>
+  <si>
+    <t>L30-2712299</t>
+  </si>
+  <si>
+    <t>L31-24492299</t>
+  </si>
+  <si>
+    <t>L32-46652299</t>
+  </si>
+  <si>
+    <t>L33-44952299</t>
+  </si>
+  <si>
+    <t>L34-34935587</t>
+  </si>
+  <si>
+    <t>L35-45863493</t>
+  </si>
+  <si>
+    <t>L36-2283493</t>
+  </si>
+  <si>
+    <t>L37-68263493</t>
+  </si>
+  <si>
+    <t>L38-75633493</t>
+  </si>
+  <si>
+    <t>L39-44273493</t>
+  </si>
+  <si>
+    <t>L40-83353493</t>
+  </si>
+  <si>
+    <t>L41-51553493</t>
+  </si>
+  <si>
+    <t>L42-2713493</t>
+  </si>
+  <si>
+    <t>L43-57763493</t>
+  </si>
+  <si>
+    <t>L44-24493493</t>
+  </si>
+  <si>
+    <t>L45-46653493</t>
+  </si>
+  <si>
+    <t>L46-44953493</t>
+  </si>
+  <si>
+    <t>L47-55874586</t>
+  </si>
+  <si>
+    <t>L48-44234586</t>
+  </si>
+  <si>
+    <t>L49-49292870</t>
+  </si>
+  <si>
+    <t>L50-4929659</t>
+  </si>
+  <si>
+    <t>L51-49291037</t>
+  </si>
+  <si>
+    <t>L52-4929659</t>
+  </si>
+  <si>
+    <t>L53-18155210</t>
+  </si>
+  <si>
+    <t>L54-18151445</t>
+  </si>
+  <si>
+    <t>L55-16167762</t>
+  </si>
+  <si>
+    <t>L56-16162520</t>
+  </si>
+  <si>
+    <t>L57-90647762</t>
+  </si>
+  <si>
+    <t>L58-906489</t>
+  </si>
+  <si>
+    <t>L59-1317659</t>
+  </si>
+  <si>
+    <t>L60-13178605</t>
+  </si>
+  <si>
+    <t>L61-86051367</t>
+  </si>
+  <si>
+    <t>L62-86058921</t>
+  </si>
+  <si>
+    <t>L63-11631676</t>
+  </si>
+  <si>
+    <t>L64-11637051</t>
+  </si>
+  <si>
+    <t>L65-9137762</t>
+  </si>
+  <si>
+    <t>L66-21077762</t>
+  </si>
+  <si>
+    <t>L67-21075996</t>
+  </si>
+  <si>
+    <t>L68-21076293</t>
+  </si>
+  <si>
+    <t>L69-9137762</t>
+  </si>
+  <si>
+    <t>L70-67048921</t>
+  </si>
+  <si>
+    <t>L71-2284586</t>
+  </si>
+  <si>
+    <t>L72-24416293</t>
+  </si>
+  <si>
+    <t>L73-9553506</t>
+  </si>
+  <si>
+    <t>L74-9558964</t>
+  </si>
+  <si>
+    <t>L75-35062908</t>
+  </si>
+  <si>
+    <t>L76-2286826</t>
+  </si>
+  <si>
+    <t>L77-2285776</t>
+  </si>
+  <si>
+    <t>L78-89646826</t>
+  </si>
+  <si>
+    <t>L79-57766826</t>
+  </si>
+  <si>
+    <t>L80-6598329</t>
+  </si>
+  <si>
+    <t>L81-6597051</t>
+  </si>
+  <si>
+    <t>L82-6599239</t>
+  </si>
+  <si>
+    <t>L83-6597960</t>
+  </si>
+  <si>
+    <t>L84-6596233</t>
+  </si>
+  <si>
+    <t>L85-6595416</t>
+  </si>
+  <si>
+    <t>L86-6596798</t>
+  </si>
+  <si>
+    <t>L87-7923279</t>
+  </si>
+  <si>
+    <t>L88-7563792</t>
+  </si>
+  <si>
+    <t>L89-7279792</t>
+  </si>
+  <si>
+    <t>L90-8335792</t>
+  </si>
+  <si>
+    <t>L91-2449792</t>
+  </si>
+  <si>
+    <t>L92-4665792</t>
+  </si>
+  <si>
+    <t>L93-4495792</t>
+  </si>
+  <si>
+    <t>L94-54162267</t>
+  </si>
+  <si>
+    <t>L95-54167637</t>
+  </si>
+  <si>
+    <t>L96-89642168</t>
+  </si>
+  <si>
+    <t>L97-36595996</t>
+  </si>
+  <si>
+    <t>L98-57625996</t>
+  </si>
+  <si>
+    <t>L99-32425097</t>
+  </si>
+  <si>
+    <t>L100-75633242</t>
+  </si>
+  <si>
+    <t>L101-44273242</t>
+  </si>
+  <si>
+    <t>L102-32427279</t>
+  </si>
+  <si>
+    <t>L103-2713242</t>
+  </si>
+  <si>
+    <t>L104-32421611</t>
+  </si>
+  <si>
+    <t>L105-50971611</t>
+  </si>
+  <si>
+    <t>L106-81818179</t>
+  </si>
+  <si>
+    <t>L107-81817762</t>
+  </si>
+  <si>
+    <t>L108-90257762</t>
+  </si>
+  <si>
+    <t>L109-75634427</t>
+  </si>
+  <si>
+    <t>L110-75637279</t>
+  </si>
+  <si>
+    <t>L111-75638335</t>
+  </si>
+  <si>
+    <t>L112-75635155</t>
+  </si>
+  <si>
+    <t>L113-7563271</t>
+  </si>
+  <si>
+    <t>L114-24497563</t>
+  </si>
+  <si>
+    <t>L115-46657563</t>
+  </si>
+  <si>
+    <t>L116-44957563</t>
+  </si>
+  <si>
+    <t>L117-75631611</t>
+  </si>
+  <si>
+    <t>L118-44277279</t>
+  </si>
+  <si>
+    <t>L119-44278335</t>
+  </si>
+  <si>
+    <t>L120-44275155</t>
+  </si>
+  <si>
+    <t>L121-4427271</t>
+  </si>
+  <si>
+    <t>L122-24494427</t>
+  </si>
+  <si>
+    <t>L123-46654427</t>
+  </si>
+  <si>
+    <t>L124-44954427</t>
+  </si>
+  <si>
+    <t>L125-44271611</t>
+  </si>
+  <si>
+    <t>L126-52101445</t>
+  </si>
+  <si>
+    <t>L127-81795509</t>
+  </si>
+  <si>
+    <t>L128-81797762</t>
+  </si>
+  <si>
+    <t>L129-72794014</t>
+  </si>
+  <si>
+    <t>L130-83357279</t>
+  </si>
+  <si>
+    <t>L131-51557279</t>
+  </si>
+  <si>
+    <t>L132-2717279</t>
+  </si>
+  <si>
+    <t>L133-24497279</t>
+  </si>
+  <si>
+    <t>L134-46657279</t>
+  </si>
+  <si>
+    <t>L135-44957279</t>
+  </si>
+  <si>
+    <t>L136-16117279</t>
+  </si>
+  <si>
+    <t>L137-55091579</t>
+  </si>
+  <si>
+    <t>L138-83351531</t>
+  </si>
+  <si>
+    <t>L139-51558335</t>
+  </si>
+  <si>
+    <t>L140-24498335</t>
+  </si>
+  <si>
+    <t>L141-46658335</t>
+  </si>
+  <si>
+    <t>L142-44958335</t>
+  </si>
+  <si>
+    <t>L143-77622268</t>
+  </si>
+  <si>
+    <t>L144-5155271</t>
+  </si>
+  <si>
+    <t>L145-51552908</t>
+  </si>
+  <si>
+    <t>L146-46655155</t>
+  </si>
+  <si>
+    <t>L147-44955155</t>
+  </si>
+  <si>
+    <t>L148-51551611</t>
+  </si>
+  <si>
+    <t>L149-2712908</t>
+  </si>
+  <si>
+    <t>L150-4665271</t>
+  </si>
+  <si>
+    <t>L151-4495271</t>
+  </si>
+  <si>
+    <t>L152-2711611</t>
+  </si>
+  <si>
+    <t>L153-15795848</t>
+  </si>
+  <si>
+    <t>L154-70518847</t>
+  </si>
+  <si>
+    <t>L155-57768229</t>
+  </si>
+  <si>
+    <t>L156-3176233</t>
+  </si>
+  <si>
+    <t>L157-46652449</t>
+  </si>
+  <si>
+    <t>L158-24494495</t>
+  </si>
+  <si>
+    <t>L159-46654495</t>
+  </si>
+  <si>
+    <t>L160-16118420</t>
+  </si>
+  <si>
+    <t>L161-78291968</t>
+  </si>
+  <si>
+    <t>L162-1815792</t>
+  </si>
+  <si>
+    <t>L163-78296826</t>
+  </si>
+  <si>
+    <t>L164-5210792</t>
+  </si>
+  <si>
+    <t>L165-1445792</t>
+  </si>
+  <si>
+    <t>L166-52107279</t>
+  </si>
+  <si>
+    <t>L167-52108335</t>
+  </si>
+  <si>
+    <t>L168-52102449</t>
+  </si>
+  <si>
+    <t>L169-52104665</t>
+  </si>
+  <si>
+    <t>L170-52104495</t>
+  </si>
+  <si>
+    <t>L171-14457279</t>
+  </si>
+  <si>
+    <t>L172-14458335</t>
+  </si>
+  <si>
+    <t>L173-78295776</t>
+  </si>
+  <si>
+    <t>L174-14452449</t>
+  </si>
+  <si>
+    <t>L175-14454665</t>
+  </si>
+  <si>
+    <t>L176-76378581</t>
+  </si>
+  <si>
+    <t>L177-58487526</t>
+  </si>
+  <si>
+    <t>L178-21545996</t>
   </si>
   <si>
     <t>pLTto(MW)</t>
@@ -346,19 +934,100 @@
     <t>pLTfrom(MW)</t>
   </si>
   <si>
-    <t>T1-324</t>
-  </si>
-  <si>
-    <t>T2-911</t>
-  </si>
-  <si>
-    <t>T3-912</t>
-  </si>
-  <si>
-    <t>T4-1011</t>
-  </si>
-  <si>
-    <t>T5-1012</t>
+    <t>T1-90246542</t>
+  </si>
+  <si>
+    <t>T2-90246542</t>
+  </si>
+  <si>
+    <t>T3-60699192</t>
+  </si>
+  <si>
+    <t>T4-60691968</t>
+  </si>
+  <si>
+    <t>T5-85742299</t>
+  </si>
+  <si>
+    <t>T6-85745587</t>
+  </si>
+  <si>
+    <t>T7-49291815</t>
+  </si>
+  <si>
+    <t>T8-67044586</t>
+  </si>
+  <si>
+    <t>T9-24413506</t>
+  </si>
+  <si>
+    <t>T10-13676826</t>
+  </si>
+  <si>
+    <t>T11-1676228</t>
+  </si>
+  <si>
+    <t>T12-6593279</t>
+  </si>
+  <si>
+    <t>T13-71802168</t>
+  </si>
+  <si>
+    <t>T14-68338964</t>
+  </si>
+  <si>
+    <t>T15-36593242</t>
+  </si>
+  <si>
+    <t>T16-81814427</t>
+  </si>
+  <si>
+    <t>T17-90257563</t>
+  </si>
+  <si>
+    <t>T18-22675210</t>
+  </si>
+  <si>
+    <t>T19-81797279</t>
+  </si>
+  <si>
+    <t>T20-55098335</t>
+  </si>
+  <si>
+    <t>T21-55091531</t>
+  </si>
+  <si>
+    <t>T22-77625155</t>
+  </si>
+  <si>
+    <t>T23-7762271</t>
+  </si>
+  <si>
+    <t>T24-83291445</t>
+  </si>
+  <si>
+    <t>T25-83291445</t>
+  </si>
+  <si>
+    <t>T26-22682908</t>
+  </si>
+  <si>
+    <t>T27-88475776</t>
+  </si>
+  <si>
+    <t>T28-88478103</t>
+  </si>
+  <si>
+    <t>T29-3172449</t>
+  </si>
+  <si>
+    <t>T30-894495</t>
+  </si>
+  <si>
+    <t>T31-25204665</t>
+  </si>
+  <si>
+    <t>T32-59968420</t>
   </si>
 </sst>
 </file>
@@ -735,16 +1404,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>1035.999966608644</v>
+        <v>9921.230099999902</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2850</v>
+        <v>5727.89</v>
       </c>
       <c r="D2">
-        <v>71164.91778268501</v>
+        <v>12940372.20164243</v>
       </c>
     </row>
   </sheetData>
@@ -754,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -770,266 +1439,981 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="B2">
-        <v>-8.8766323781621</v>
+        <v>0.2961112905555199</v>
       </c>
       <c r="C2">
-        <v>1.001413839402157</v>
+        <v>0.925218131468633</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>2</v>
+        <v>228</v>
       </c>
       <c r="B3">
-        <v>-8.951800829564231</v>
+        <v>0.1538880399937057</v>
       </c>
       <c r="C3">
-        <v>1.001475011255603</v>
+        <v>0.9929969819195416</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="B4">
-        <v>-5.487371811639138</v>
+        <v>-0.3608599689553336</v>
       </c>
       <c r="C4">
-        <v>1.004517028842937</v>
+        <v>0.9895571435435925</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>4</v>
+        <v>317</v>
       </c>
       <c r="B5">
-        <v>-9.03202637144938</v>
+        <v>0.4702591975946078</v>
       </c>
       <c r="C5">
-        <v>0.9955034258093148</v>
+        <v>0.9269795306388107</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>5</v>
+        <v>659</v>
       </c>
       <c r="B6">
-        <v>-9.907449876801424</v>
+        <v>0.4430062918524289</v>
       </c>
       <c r="C6">
-        <v>1.008260639452845</v>
+        <v>0.9269415762903974</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>6</v>
+        <v>792</v>
       </c>
       <c r="B7">
-        <v>-10.81448999019221</v>
+        <v>-0.7602610174423516</v>
       </c>
       <c r="C7">
-        <v>1.02108918284511</v>
+        <v>0.9492382783342267</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>7</v>
+        <v>913</v>
       </c>
       <c r="B8">
-        <v>-12.58769810735618</v>
+        <v>0.9436058674028991</v>
       </c>
       <c r="C8">
-        <v>1.005137416644855</v>
+        <v>0.92673515948356</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>8</v>
+        <v>955</v>
       </c>
       <c r="B9">
-        <v>-12.41642201878874</v>
+        <v>-0.4179266521380864</v>
       </c>
       <c r="C9">
-        <v>0.9957319463857712</v>
+        <v>0.984165378621187</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>9</v>
+        <v>1037</v>
       </c>
       <c r="B10">
-        <v>-6.708215458150161</v>
+        <v>0.1679592592057642</v>
       </c>
       <c r="C10">
-        <v>1.008275135462243</v>
+        <v>0.9266974120270424</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>10</v>
+        <v>1163</v>
       </c>
       <c r="B11">
-        <v>-8.860194665532488</v>
+        <v>0.1894503805430794</v>
       </c>
       <c r="C11">
-        <v>1.031492285646338</v>
+        <v>0.9255095434531876</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>11</v>
+        <v>1317</v>
       </c>
       <c r="B12">
-        <v>-2.965646368623914</v>
+        <v>0.3001953408620207</v>
       </c>
       <c r="C12">
-        <v>0.9874233156367803</v>
+        <v>0.9262959935734039</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>12</v>
+        <v>1367</v>
       </c>
       <c r="B13">
-        <v>-2.766778085211983</v>
+        <v>0.7400259883300795</v>
       </c>
       <c r="C13">
-        <v>0.9915776847629607</v>
+        <v>0.9264512189585825</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>13</v>
+        <v>1445</v>
       </c>
       <c r="B14">
-        <v>1.717228750155294E-32</v>
+        <v>-0.5603814621591153</v>
       </c>
       <c r="C14">
-        <v>1.000879236114013</v>
+        <v>0.9515854029377239</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>14</v>
+        <v>1531</v>
       </c>
       <c r="B15">
-        <v>-0.6665560249641195</v>
+        <v>-0.2805361475860585</v>
       </c>
       <c r="C15">
-        <v>0.9782038935085714</v>
+        <v>0.9721035284392686</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>15</v>
+        <v>1579</v>
       </c>
       <c r="B16">
-        <v>2.861265928563993</v>
+        <v>0.170799117194083</v>
       </c>
       <c r="C16">
-        <v>0.9865755010586286</v>
+        <v>0.9263847275098488</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>16</v>
+        <v>1611</v>
       </c>
       <c r="B17">
-        <v>2.523351346686917</v>
+        <v>-1.424260146815369</v>
       </c>
       <c r="C17">
-        <v>0.9848875870736138</v>
+        <v>0.9971956869530518</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>17</v>
+        <v>1616</v>
       </c>
       <c r="B18">
-        <v>3.915959082307656</v>
+        <v>0.3336970800602753</v>
       </c>
       <c r="C18">
-        <v>0.9918159198704417</v>
+        <v>0.9257702825903044</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>18</v>
+        <v>1676</v>
       </c>
       <c r="B19">
-        <v>4.461299950074305</v>
+        <v>0.1882818853679724</v>
       </c>
       <c r="C19">
-        <v>0.991871097192813</v>
+        <v>0.9254956791471611</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>19</v>
+        <v>1815</v>
       </c>
       <c r="B20">
-        <v>2.428552765779183</v>
+        <v>-0.3431086140335894</v>
       </c>
       <c r="C20">
-        <v>0.9854249485856689</v>
+        <v>0.9321365778199988</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>20</v>
+        <v>1968</v>
       </c>
       <c r="B21">
-        <v>2.858991087720517</v>
+        <v>-0.3168492651942059</v>
       </c>
       <c r="C21">
-        <v>0.98673960100978</v>
+        <v>1.003161093440566</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>21</v>
+        <v>2107</v>
       </c>
       <c r="B22">
-        <v>4.538313520596536</v>
+        <v>0.934950580444084</v>
       </c>
       <c r="C22">
-        <v>0.9932270240698891</v>
+        <v>0.9265967351279794</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>22</v>
+        <v>2154</v>
       </c>
       <c r="B23">
-        <v>5.642315580810013</v>
+        <v>0.5300711691988188</v>
       </c>
       <c r="C23">
-        <v>1.00542993921545</v>
+        <v>0.9264095788064117</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>23</v>
+        <v>2168</v>
       </c>
       <c r="B24">
-        <v>3.354995304291808</v>
+        <v>-0.3335186939541259</v>
       </c>
       <c r="C24">
-        <v>0.9876208047137668</v>
+        <v>1.004635338896452</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>24</v>
+        <v>2267</v>
       </c>
       <c r="B25">
-        <v>-0.3079678329274433</v>
+        <v>0.4958930024095658</v>
       </c>
       <c r="C25">
-        <v>0.9780814001805032</v>
+        <v>0.9259222815099585</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>2268</v>
+      </c>
+      <c r="B26">
+        <v>0.09104017028979981</v>
+      </c>
+      <c r="C26">
+        <v>0.9252935258683875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>2299</v>
+      </c>
+      <c r="B27">
+        <v>0.05679248389674412</v>
+      </c>
+      <c r="C27">
+        <v>0.9954741903254093</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>2441</v>
+      </c>
+      <c r="B28">
+        <v>-0.3597392681863164</v>
+      </c>
+      <c r="C28">
+        <v>0.9249075437716259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>2449</v>
+      </c>
+      <c r="B29">
+        <v>-0.2525396383478827</v>
+      </c>
+      <c r="C29">
+        <v>0.9879697704917642</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>2520</v>
+      </c>
+      <c r="B30">
+        <v>0.2967841932659487</v>
+      </c>
+      <c r="C30">
+        <v>0.9255936406129008</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>2870</v>
+      </c>
+      <c r="B31">
+        <v>0.1683010784630192</v>
+      </c>
+      <c r="C31">
+        <v>0.9267026016602342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>2908</v>
+      </c>
+      <c r="B32">
+        <v>-0.327508627423605</v>
+      </c>
+      <c r="C32">
+        <v>0.9886083929484601</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>3097</v>
+      </c>
+      <c r="B33">
+        <v>0.2154918546769559</v>
+      </c>
+      <c r="C33">
+        <v>0.9260480463999587</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>3242</v>
+      </c>
+      <c r="B34">
+        <v>-2.320729854341349</v>
+      </c>
+      <c r="C34">
+        <v>0.9982478182125727</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>3279</v>
+      </c>
+      <c r="B35">
+        <v>-0.759818996040133</v>
+      </c>
+      <c r="C35">
+        <v>0.9492009994709483</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>3493</v>
+      </c>
+      <c r="B36">
+        <v>0.08435327176721795</v>
+      </c>
+      <c r="C36">
+        <v>0.9915950176691127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>3506</v>
+      </c>
+      <c r="B37">
+        <v>-0.4180832484152832</v>
+      </c>
+      <c r="C37">
+        <v>0.9841333274507695</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>3659</v>
+      </c>
+      <c r="B38">
+        <v>1.003758707594244</v>
+      </c>
+      <c r="C38">
+        <v>0.9266694731272398</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>4014</v>
+      </c>
+      <c r="B39">
+        <v>-0.3703966488325959</v>
+      </c>
+      <c r="C39">
+        <v>0.9841982626614934</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>4423</v>
+      </c>
+      <c r="B40">
+        <v>0.05775518002752301</v>
+      </c>
+      <c r="C40">
+        <v>0.9954645703953297</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>4427</v>
+      </c>
+      <c r="B41">
+        <v>-0.1782310140387346</v>
+      </c>
+      <c r="C41">
+        <v>0.9943217605317397</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>4495</v>
+      </c>
+      <c r="B42">
+        <v>0.001368131132909995</v>
+      </c>
+      <c r="C42">
+        <v>0.9935773297782234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>4586</v>
+      </c>
+      <c r="B43">
+        <v>0.3050281413020497</v>
+      </c>
+      <c r="C43">
+        <v>0.9948315249919319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>4665</v>
+      </c>
+      <c r="B44">
+        <v>-0.03065717347297346</v>
+      </c>
+      <c r="C44">
+        <v>0.9925266826890161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>4929</v>
+      </c>
+      <c r="B45">
+        <v>0.1708564981437607</v>
+      </c>
+      <c r="C45">
+        <v>0.9267488144833724</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>5097</v>
+      </c>
+      <c r="B46">
+        <v>-2.324086846907638</v>
+      </c>
+      <c r="C46">
+        <v>0.9982620976613212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>5155</v>
+      </c>
+      <c r="B47">
+        <v>-0.3735301361107961</v>
+      </c>
+      <c r="C47">
+        <v>0.995556823604088</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>5210</v>
+      </c>
+      <c r="B48">
+        <v>-0.7105413645692628</v>
+      </c>
+      <c r="C48">
+        <v>0.9535572977851761</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>5416</v>
+      </c>
+      <c r="B49">
+        <v>0.3811358201241792</v>
+      </c>
+      <c r="C49">
+        <v>0.9258365931030709</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>5509</v>
+      </c>
+      <c r="B50">
+        <v>0.1467467202184486</v>
+      </c>
+      <c r="C50">
+        <v>0.9268817316124667</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>5587</v>
+      </c>
+      <c r="B51">
+        <v>0.08565943677955577</v>
+      </c>
+      <c r="C51">
+        <v>0.9915709207726574</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>5762</v>
+      </c>
+      <c r="B52">
+        <v>0.7287894572782664</v>
+      </c>
+      <c r="C52">
+        <v>0.926344635561254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>5776</v>
+      </c>
+      <c r="B53">
+        <v>0.07532223124041203</v>
+      </c>
+      <c r="C53">
+        <v>1.006969820596207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>5848</v>
+      </c>
+      <c r="B54">
+        <v>0.174338062356401</v>
+      </c>
+      <c r="C54">
+        <v>0.9261832713961069</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>5996</v>
+      </c>
+      <c r="B55">
+        <v>0.7819190761662261</v>
+      </c>
+      <c r="C55">
+        <v>0.9263576019319453</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>6069</v>
+      </c>
+      <c r="B56">
+        <v>-0.2410461636635993</v>
+      </c>
+      <c r="C56">
+        <v>0.9243591890438297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>6233</v>
+      </c>
+      <c r="B57">
+        <v>0.4887715839943167</v>
+      </c>
+      <c r="C57">
+        <v>0.9270087644192746</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>6293</v>
+      </c>
+      <c r="B58">
+        <v>-0.2987236177197204</v>
+      </c>
+      <c r="C58">
+        <v>0.9248829035459697</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>6542</v>
+      </c>
+      <c r="B59">
+        <v>-0.3172214337893986</v>
+      </c>
+      <c r="C59">
+        <v>0.9336621043714427</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>6704</v>
+      </c>
+      <c r="B60">
+        <v>0.3393539352778724</v>
+      </c>
+      <c r="C60">
+        <v>0.9255188397633044</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>6798</v>
+      </c>
+      <c r="B61">
+        <v>0.5052223323967459</v>
+      </c>
+      <c r="C61">
+        <v>0.9270045134332215</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>6826</v>
+      </c>
+      <c r="B62">
+        <v>0.09150001866098473</v>
+      </c>
+      <c r="C62">
+        <v>1.00617798643278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>6833</v>
+      </c>
+      <c r="B63">
+        <v>-0.2549518211730422</v>
+      </c>
+      <c r="C63">
+        <v>0.9230689110680568</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>7051</v>
+      </c>
+      <c r="B64">
+        <v>0.1894618105002258</v>
+      </c>
+      <c r="C64">
+        <v>0.9255281193009006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>7180</v>
+      </c>
+      <c r="B65">
+        <v>-0.2636468689796266</v>
+      </c>
+      <c r="C65">
+        <v>0.9243629314491059</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>7279</v>
+      </c>
+      <c r="B66">
+        <v>-0.3685605098731544</v>
+      </c>
+      <c r="C66">
+        <v>0.9842049627771939</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>7526</v>
+      </c>
+      <c r="B67">
+        <v>0.1762273183955984</v>
+      </c>
+      <c r="C67">
+        <v>0.9260623095381184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>7563</v>
+      </c>
+      <c r="B68">
+        <v>-0.6418186067760924</v>
+      </c>
+      <c r="C68">
+        <v>0.9896172615123615</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>7637</v>
+      </c>
+      <c r="B69">
+        <v>0.2480477490591123</v>
+      </c>
+      <c r="C69">
+        <v>0.9250857160636359</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>7762</v>
+      </c>
+      <c r="B70">
+        <v>0.4187566438390534</v>
+      </c>
+      <c r="C70">
+        <v>0.9260087354939838</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>7829</v>
+      </c>
+      <c r="B71">
+        <v>0.005410415859063469</v>
+      </c>
+      <c r="C71">
+        <v>1.006634426897462</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>7960</v>
+      </c>
+      <c r="B72">
+        <v>0.4787361898565953</v>
+      </c>
+      <c r="C72">
+        <v>0.9269608045819563</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>8103</v>
+      </c>
+      <c r="B73">
+        <v>0.1385383105964981</v>
+      </c>
+      <c r="C73">
+        <v>0.9149531039262291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>8179</v>
+      </c>
+      <c r="B74">
+        <v>0.2283074631068333</v>
+      </c>
+      <c r="C74">
+        <v>0.9257677612894942</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>8181</v>
+      </c>
+      <c r="B75">
+        <v>0.2593795463082474</v>
+      </c>
+      <c r="C75">
+        <v>0.9255614023703356</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>8229</v>
+      </c>
+      <c r="B76">
+        <v>0.07520583506405895</v>
+      </c>
+      <c r="C76">
+        <v>1.006967114989388</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>8329</v>
+      </c>
+      <c r="B77">
+        <v>0.3426547893617269</v>
+      </c>
+      <c r="C77">
+        <v>0.9263351738735333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>8335</v>
+      </c>
+      <c r="B78">
+        <v>-0.2807044737844356</v>
+      </c>
+      <c r="C78">
+        <v>0.9721333131839545</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>8420</v>
+      </c>
+      <c r="B79">
+        <v>-1.421730430716369</v>
+      </c>
+      <c r="C79">
+        <v>0.9972143979493813</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>8574</v>
+      </c>
+      <c r="B80">
+        <v>0.3099011496068941</v>
+      </c>
+      <c r="C80">
+        <v>0.9257958825529656</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>8581</v>
+      </c>
+      <c r="B81">
+        <v>0.1891130031826074</v>
+      </c>
+      <c r="C81">
+        <v>0.9246492194750676</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>8605</v>
+      </c>
+      <c r="B82">
+        <v>0.7612925832409468</v>
+      </c>
+      <c r="C82">
+        <v>0.9264837862033595</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>8847</v>
+      </c>
+      <c r="B83">
+        <v>0.1796990464557524</v>
+      </c>
+      <c r="C83">
+        <v>0.9253306185859764</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>8921</v>
+      </c>
+      <c r="B84">
+        <v>0.3645846720732112</v>
+      </c>
+      <c r="C84">
+        <v>0.9257708106263207</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>8964</v>
+      </c>
+      <c r="B85">
+        <v>-0.3336124648170414</v>
+      </c>
+      <c r="C85">
+        <v>1.004646869337655</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>9024</v>
+      </c>
+      <c r="B86">
+        <v>-0.0928475275039027</v>
+      </c>
+      <c r="C86">
+        <v>0.9276269760087874</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>9025</v>
+      </c>
+      <c r="B87">
+        <v>0.274223002558808</v>
+      </c>
+      <c r="C87">
+        <v>0.9255664964660715</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
+        <v>9064</v>
+      </c>
+      <c r="B88">
+        <v>0.3274920117440985</v>
+      </c>
+      <c r="C88">
+        <v>0.9257295694064193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>9192</v>
+      </c>
+      <c r="B89">
+        <v>-0.3169495949187805</v>
+      </c>
+      <c r="C89">
+        <v>1.002730795312403</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>9239</v>
+      </c>
+      <c r="B90">
+        <v>0.4798638818278276</v>
+      </c>
+      <c r="C90">
+        <v>0.9269596771892366</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1064,16 +2448,16 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>1037</v>
       </c>
       <c r="C2">
-        <v>108</v>
+        <v>-0</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1081,16 +2465,16 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>1163</v>
       </c>
       <c r="C3">
-        <v>195</v>
+        <v>-0</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>-0</v>
       </c>
       <c r="E3">
-        <v>0.605</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1098,16 +2482,16 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>1317</v>
       </c>
       <c r="C4">
-        <v>265</v>
+        <v>149.3</v>
       </c>
       <c r="D4">
-        <v>54</v>
+        <v>-2</v>
       </c>
       <c r="E4">
-        <v>0.223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1115,16 +2499,16 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>1367</v>
       </c>
       <c r="C5">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>-0</v>
       </c>
       <c r="E5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1132,16 +2516,16 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>1445</v>
       </c>
       <c r="C6">
-        <v>317</v>
+        <v>238.4</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>210.9</v>
       </c>
       <c r="E6">
-        <v>0.149</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1149,16 +2533,16 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>1531</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>-0</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.367</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1166,16 +2550,16 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>1579</v>
       </c>
       <c r="C8">
-        <v>333</v>
+        <v>-0</v>
       </c>
       <c r="D8">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0.142</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1183,16 +2567,16 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>1611</v>
       </c>
       <c r="C9">
-        <v>181</v>
+        <v>274.1</v>
       </c>
       <c r="D9">
-        <v>37</v>
+        <v>166.5</v>
       </c>
       <c r="E9">
-        <v>0.241</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1200,16 +2584,16 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1616</v>
       </c>
       <c r="C10">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.572</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1217,16 +2601,16 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>1676</v>
       </c>
       <c r="C11">
-        <v>128</v>
+        <v>-0</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.318</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1234,16 +2618,16 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1815</v>
       </c>
       <c r="C12">
-        <v>180</v>
+        <v>63.66</v>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E12">
-        <v>0.329</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1251,16 +2635,16 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>1968</v>
       </c>
       <c r="C13">
-        <v>74</v>
+        <v>118.4</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="E13">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1268,16 +2652,16 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>2107</v>
       </c>
       <c r="C14">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0.629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1285,16 +2669,16 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>2154</v>
       </c>
       <c r="C15">
-        <v>136</v>
+        <v>-357.45</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>33.05</v>
       </c>
       <c r="E15">
-        <v>0.541</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1302,16 +2686,16 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>2168</v>
       </c>
       <c r="C16">
-        <v>125</v>
+        <v>8.6</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>-1.48</v>
       </c>
       <c r="E16">
-        <v>0.607</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1319,16 +2703,16 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>2267</v>
       </c>
       <c r="C17">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.573</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1336,16 +2720,1240 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>2268</v>
       </c>
       <c r="C18">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="D18">
+        <v>-0</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>228</v>
+      </c>
+      <c r="C19">
+        <v>-23.43</v>
+      </c>
+      <c r="D19">
+        <v>57.4</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>2299</v>
+      </c>
+      <c r="C20">
+        <v>402.1</v>
+      </c>
+      <c r="D20">
+        <v>110.2</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>2441</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>-0</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>2449</v>
+      </c>
+      <c r="C22">
+        <v>301.9</v>
+      </c>
+      <c r="D22">
+        <v>-103.2</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>2520</v>
+      </c>
+      <c r="C23">
+        <v>-0</v>
+      </c>
+      <c r="D23">
+        <v>-0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>271</v>
+      </c>
+      <c r="C24">
+        <v>96.7</v>
+      </c>
+      <c r="D24">
+        <v>26.8</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>2870</v>
+      </c>
+      <c r="C25">
+        <v>-0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>2908</v>
+      </c>
+      <c r="C26">
+        <v>203.8</v>
+      </c>
+      <c r="D26">
+        <v>61</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="E18">
-        <v>0.412</v>
+      <c r="B27">
+        <v>3097</v>
+      </c>
+      <c r="C27">
+        <v>361.91</v>
+      </c>
+      <c r="D27">
+        <v>3.66</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>317</v>
+      </c>
+      <c r="C28">
+        <v>-0</v>
+      </c>
+      <c r="D28">
+        <v>-0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
+        <v>3242</v>
+      </c>
+      <c r="C29">
+        <v>296.1</v>
+      </c>
+      <c r="D29">
+        <v>82.3</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <v>3279</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>3493</v>
+      </c>
+      <c r="C31">
+        <v>226.3</v>
+      </c>
+      <c r="D31">
+        <v>61.1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>3506</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>3659</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>4014</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
+        <v>4423</v>
+      </c>
+      <c r="C35">
+        <v>-0</v>
+      </c>
+      <c r="D35">
+        <v>-0</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36">
+        <v>4427</v>
+      </c>
+      <c r="C36">
+        <v>296.8</v>
+      </c>
+      <c r="D36">
+        <v>77.7</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
+        <v>4495</v>
+      </c>
+      <c r="C37">
+        <v>336.3</v>
+      </c>
+      <c r="D37">
+        <v>104.4</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38">
+        <v>4586</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>4665</v>
+      </c>
+      <c r="C39">
+        <v>390.5</v>
+      </c>
+      <c r="D39">
+        <v>62.5</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40">
+        <v>4929</v>
+      </c>
+      <c r="C40">
+        <v>37</v>
+      </c>
+      <c r="D40">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>5097</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>5155</v>
+      </c>
+      <c r="C42">
+        <v>411.3000000000001</v>
+      </c>
+      <c r="D42">
+        <v>168</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43">
+        <v>5210</v>
+      </c>
+      <c r="C43">
+        <v>347.61</v>
+      </c>
+      <c r="D43">
+        <v>74.37</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44">
+        <v>5416</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45">
+        <v>5509</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46">
+        <v>5587</v>
+      </c>
+      <c r="C46">
+        <v>-0</v>
+      </c>
+      <c r="D46">
+        <v>-0</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47">
+        <v>5762</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48">
+        <v>5776</v>
+      </c>
+      <c r="C48">
+        <v>222.7</v>
+      </c>
+      <c r="D48">
+        <v>80.5</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49">
+        <v>5848</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>-0</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50">
+        <v>5996</v>
+      </c>
+      <c r="C50">
+        <v>-0</v>
+      </c>
+      <c r="D50">
+        <v>-0</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51">
+        <v>6069</v>
+      </c>
+      <c r="C51">
+        <v>-456.66</v>
+      </c>
+      <c r="D51">
+        <v>-131.97</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52">
+        <v>6233</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53">
+        <v>6293</v>
+      </c>
+      <c r="C53">
+        <v>-0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54">
+        <v>6542</v>
+      </c>
+      <c r="C54">
+        <v>355.98</v>
+      </c>
+      <c r="D54">
+        <v>-147.98</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55">
+        <v>659</v>
+      </c>
+      <c r="C55">
+        <v>-0</v>
+      </c>
+      <c r="D55">
+        <v>-0</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56">
+        <v>6704</v>
+      </c>
+      <c r="C56">
+        <v>-0</v>
+      </c>
+      <c r="D56">
+        <v>-0</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57">
+        <v>6798</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58">
+        <v>6826</v>
+      </c>
+      <c r="C58">
+        <v>326.9</v>
+      </c>
+      <c r="D58">
+        <v>-82.3</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59">
+        <v>6833</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60">
+        <v>7051</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61">
+        <v>7180</v>
+      </c>
+      <c r="C61">
+        <v>-0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62">
+        <v>7279</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63">
+        <v>7526</v>
+      </c>
+      <c r="C63">
+        <v>-179.73</v>
+      </c>
+      <c r="D63">
+        <v>-63.08000000000001</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64">
+        <v>7563</v>
+      </c>
+      <c r="C64">
+        <v>531.7</v>
+      </c>
+      <c r="D64">
+        <v>-12.8</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65">
+        <v>7637</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66">
+        <v>7762</v>
+      </c>
+      <c r="C66">
+        <v>-0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67">
+        <v>7829</v>
+      </c>
+      <c r="C67">
+        <v>-114.36</v>
+      </c>
+      <c r="D67">
+        <v>30.04</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68">
+        <v>792</v>
+      </c>
+      <c r="C68">
+        <v>295.3</v>
+      </c>
+      <c r="D68">
+        <v>41.9</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69">
+        <v>7960</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70">
+        <v>8103</v>
+      </c>
+      <c r="C70">
+        <v>39.34</v>
+      </c>
+      <c r="D70">
+        <v>-10.7</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71">
+        <v>8179</v>
+      </c>
+      <c r="C71">
+        <v>-0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72">
+        <v>8181</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>-0</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73">
+        <v>8229</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74">
+        <v>8329</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75">
+        <v>8335</v>
+      </c>
+      <c r="C75">
+        <v>637.92</v>
+      </c>
+      <c r="D75">
+        <v>139.57</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76">
+        <v>8420</v>
+      </c>
+      <c r="C76">
+        <v>-0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77">
+        <v>8574</v>
+      </c>
+      <c r="C77">
+        <v>-0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78">
+        <v>8581</v>
+      </c>
+      <c r="C78">
+        <v>-1299.13</v>
+      </c>
+      <c r="D78">
+        <v>-140.85</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79">
+        <v>8605</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80">
+        <v>8847</v>
+      </c>
+      <c r="C80">
+        <v>-0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81">
+        <v>89</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82">
+        <v>8921</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83">
+        <v>8964</v>
+      </c>
+      <c r="C83">
+        <v>925.91</v>
+      </c>
+      <c r="D83">
+        <v>147.97</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84">
+        <v>9024</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85">
+        <v>9025</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>-0</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86">
+        <v>9064</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>-0</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87">
+        <v>913</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88">
+        <v>9192</v>
+      </c>
+      <c r="C88">
+        <v>17.92</v>
+      </c>
+      <c r="D88">
+        <v>23.3</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89">
+        <v>9239</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90">
+        <v>955</v>
+      </c>
+      <c r="C90">
+        <v>244.2</v>
+      </c>
+      <c r="D90">
+        <v>152.7</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1355,7 +3963,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1366,883 +3974,337 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>913</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>566.67</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>1700</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>1700</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-269.94</v>
       </c>
       <c r="H2">
-        <v>3.994</v>
+        <v>-0.252</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>772.11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>7960</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-93.22</v>
       </c>
       <c r="H3">
-        <v>9.981999999999999</v>
+        <v>-1.296</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>274.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>8605</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="H4">
-        <v>9.981999999999999</v>
+        <v>-1.071</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>273.94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>9239</v>
       </c>
       <c r="C5">
-        <v>69</v>
+        <v>200</v>
       </c>
       <c r="E5">
-        <v>69</v>
+        <v>600</v>
       </c>
       <c r="F5">
-        <v>197</v>
+        <v>600</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-93.22</v>
       </c>
       <c r="H5">
-        <v>14.796</v>
+        <v>-1.296</v>
       </c>
       <c r="I5">
-        <v>80</v>
+        <v>274.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>2107</v>
       </c>
       <c r="C6">
-        <v>69</v>
+        <v>500</v>
       </c>
       <c r="E6">
-        <v>69</v>
+        <v>1500</v>
       </c>
       <c r="F6">
-        <v>197</v>
+        <v>1500</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>-257.62</v>
       </c>
       <c r="H6">
-        <v>14.796</v>
+        <v>-0.628</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>661.9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>2267</v>
       </c>
       <c r="C7">
-        <v>69</v>
+        <v>166.67</v>
       </c>
       <c r="E7">
-        <v>69</v>
+        <v>500</v>
       </c>
       <c r="F7">
-        <v>197</v>
+        <v>500</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-78.83</v>
       </c>
       <c r="H7">
-        <v>14.796</v>
+        <v>1.082</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>228.16</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>3659</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>666.67</v>
       </c>
       <c r="E8">
-        <v>-0</v>
+        <v>2000</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G8">
-        <v>-50</v>
+        <v>-282.01</v>
       </c>
       <c r="H8">
-        <v>-24.864</v>
+        <v>3.237</v>
       </c>
       <c r="I8">
-        <v>200</v>
+        <v>943.6399999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>4586</v>
       </c>
       <c r="C9">
-        <v>2.4</v>
+        <v>-727.6</v>
       </c>
       <c r="E9">
-        <v>2.4</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-29.81</v>
       </c>
       <c r="H9">
-        <v>2.891</v>
+        <v>-0.344</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>5097</v>
       </c>
       <c r="C10">
-        <v>2.4</v>
+        <v>7.08</v>
       </c>
       <c r="E10">
-        <v>2.4</v>
+        <v>21.23</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>21.23</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-4.11</v>
       </c>
       <c r="H10">
-        <v>2.891</v>
+        <v>4.98</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>6233</v>
       </c>
       <c r="C11">
-        <v>2.4</v>
+        <v>400</v>
       </c>
       <c r="E11">
-        <v>2.4</v>
+        <v>1200</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-189.97</v>
       </c>
       <c r="H11">
-        <v>2.891</v>
+        <v>-0.337</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>545.6799999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>6798</v>
       </c>
       <c r="C12">
-        <v>2.4</v>
+        <v>333.33</v>
       </c>
       <c r="E12">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-183.48</v>
       </c>
       <c r="H12">
-        <v>2.891</v>
+        <v>-0.747</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>429.61</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>7279</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>-908.9299999999999</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-6.64</v>
       </c>
       <c r="H13">
-        <v>3.994</v>
+        <v>-2.919</v>
       </c>
       <c r="I13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>2.4</v>
-      </c>
-      <c r="E14">
-        <v>2.4</v>
-      </c>
-      <c r="F14">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>2.891</v>
-      </c>
-      <c r="I14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>54.29999999999999</v>
-      </c>
-      <c r="E15">
-        <v>54.3</v>
-      </c>
-      <c r="F15">
-        <v>155</v>
-      </c>
-      <c r="G15">
-        <v>-50</v>
-      </c>
-      <c r="H15">
-        <v>-20.821</v>
-      </c>
-      <c r="I15">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>54.29999999999999</v>
-      </c>
-      <c r="E16">
-        <v>54.3</v>
-      </c>
-      <c r="F16">
-        <v>155</v>
-      </c>
-      <c r="G16">
-        <v>-50</v>
-      </c>
-      <c r="H16">
-        <v>-22.079</v>
-      </c>
-      <c r="I16">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17">
-        <v>18</v>
-      </c>
-      <c r="C17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>100</v>
-      </c>
-      <c r="F17">
-        <v>400</v>
-      </c>
-      <c r="G17">
-        <v>-50</v>
-      </c>
-      <c r="H17">
-        <v>-13.457</v>
-      </c>
-      <c r="I17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18">
-        <v>21</v>
-      </c>
-      <c r="C18">
-        <v>100</v>
-      </c>
-      <c r="E18">
-        <v>100</v>
-      </c>
-      <c r="F18">
-        <v>400</v>
-      </c>
-      <c r="G18">
-        <v>-50</v>
-      </c>
-      <c r="H18">
-        <v>-13.931</v>
-      </c>
-      <c r="I18">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>10</v>
-      </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>50</v>
-      </c>
-      <c r="G19">
-        <v>-10</v>
-      </c>
-      <c r="H19">
-        <v>0.954</v>
-      </c>
-      <c r="I19">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20">
-        <v>22</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>50</v>
-      </c>
-      <c r="G20">
-        <v>-10</v>
-      </c>
-      <c r="H20">
-        <v>0.954</v>
-      </c>
-      <c r="I20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21">
-        <v>22</v>
-      </c>
-      <c r="C21">
-        <v>10</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>50</v>
-      </c>
-      <c r="G21">
-        <v>-10</v>
-      </c>
-      <c r="H21">
-        <v>0.954</v>
-      </c>
-      <c r="I21">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22">
-        <v>22</v>
-      </c>
-      <c r="C22">
-        <v>10</v>
-      </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>50</v>
-      </c>
-      <c r="G22">
-        <v>-10</v>
-      </c>
-      <c r="H22">
-        <v>0.954</v>
-      </c>
-      <c r="I22">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23">
-        <v>10</v>
-      </c>
-      <c r="E23">
-        <v>10</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>-10</v>
-      </c>
-      <c r="H23">
-        <v>0.954</v>
-      </c>
-      <c r="I23">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>15.2</v>
-      </c>
-      <c r="E24">
-        <v>15.2</v>
-      </c>
-      <c r="F24">
-        <v>76</v>
-      </c>
-      <c r="G24">
-        <v>-25</v>
-      </c>
-      <c r="H24">
-        <v>-15.55</v>
-      </c>
-      <c r="I24">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25">
-        <v>22</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>50</v>
-      </c>
-      <c r="G25">
-        <v>-10</v>
-      </c>
-      <c r="H25">
-        <v>0.954</v>
-      </c>
-      <c r="I25">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26">
-        <v>23</v>
-      </c>
-      <c r="C26">
-        <v>54.29999999999999</v>
-      </c>
-      <c r="E26">
-        <v>54.3</v>
-      </c>
-      <c r="F26">
-        <v>155</v>
-      </c>
-      <c r="G26">
-        <v>-50</v>
-      </c>
-      <c r="H26">
-        <v>-28.2</v>
-      </c>
-      <c r="I26">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27">
-        <v>23</v>
-      </c>
-      <c r="C27">
-        <v>54.29999999999999</v>
-      </c>
-      <c r="E27">
-        <v>54.3</v>
-      </c>
-      <c r="F27">
-        <v>155</v>
-      </c>
-      <c r="G27">
-        <v>-50</v>
-      </c>
-      <c r="H27">
-        <v>-28.2</v>
-      </c>
-      <c r="I27">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28">
-        <v>140</v>
-      </c>
-      <c r="E28">
-        <v>140</v>
-      </c>
-      <c r="F28">
-        <v>350</v>
-      </c>
-      <c r="G28">
-        <v>-25</v>
-      </c>
-      <c r="H28">
-        <v>-1.859</v>
-      </c>
-      <c r="I28">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>15.2</v>
-      </c>
-      <c r="E29">
-        <v>15.2</v>
-      </c>
-      <c r="F29">
-        <v>76</v>
-      </c>
-      <c r="G29">
-        <v>-25</v>
-      </c>
-      <c r="H29">
-        <v>-15.55</v>
-      </c>
-      <c r="I29">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30">
-        <v>16</v>
-      </c>
-      <c r="E30">
-        <v>16</v>
-      </c>
-      <c r="F30">
-        <v>20</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>3.987</v>
-      </c>
-      <c r="I30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31">
-        <v>16</v>
-      </c>
-      <c r="E31">
-        <v>16</v>
-      </c>
-      <c r="F31">
-        <v>20</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>3.987</v>
-      </c>
-      <c r="I31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>15.2</v>
-      </c>
-      <c r="E32">
-        <v>15.2</v>
-      </c>
-      <c r="F32">
-        <v>76</v>
-      </c>
-      <c r="G32">
-        <v>-25</v>
-      </c>
-      <c r="H32">
-        <v>-15.606</v>
-      </c>
-      <c r="I32">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>15.2</v>
-      </c>
-      <c r="E33">
-        <v>15.2</v>
-      </c>
-      <c r="F33">
-        <v>76</v>
-      </c>
-      <c r="G33">
-        <v>-25</v>
-      </c>
-      <c r="H33">
-        <v>-15.606</v>
-      </c>
-      <c r="I33">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34">
-        <v>7</v>
-      </c>
-      <c r="C34">
-        <v>25</v>
-      </c>
-      <c r="E34">
-        <v>25</v>
-      </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>9.981999999999999</v>
-      </c>
-      <c r="I34">
-        <v>60</v>
+        <v>14.78</v>
       </c>
     </row>
   </sheetData>
@@ -2263,25 +4325,25 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2291,7 +4353,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2299,679 +4361,3579 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3097</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>659</v>
       </c>
       <c r="D2">
-        <v>-9.06491579742398</v>
+        <v>38.15962522705048</v>
       </c>
       <c r="E2">
-        <v>9.067164999838626</v>
+        <v>-38.1469324128248</v>
       </c>
       <c r="F2">
-        <v>0.002249202414647544</v>
+        <v>0.01269281422568436</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>9024</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4929</v>
       </c>
       <c r="D3">
-        <v>26.95377887122049</v>
+        <v>16.82208082313528</v>
       </c>
       <c r="E3">
-        <v>-26.54891993851434</v>
+        <v>-16.81521541447582</v>
       </c>
       <c r="F3">
-        <v>0.404858932706148</v>
+        <v>0.006865408659462169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>1815</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6542</v>
       </c>
       <c r="D4">
-        <v>-18.13199324868041</v>
+        <v>1.182740284239968</v>
       </c>
       <c r="E4">
-        <v>18.23896436268143</v>
+        <v>-1.181767449918566</v>
       </c>
       <c r="F4">
-        <v>0.1069711140010116</v>
+        <v>0.0009728343214020219</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>6542</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1445</v>
       </c>
       <c r="D5">
-        <v>-2.170757884892138</v>
+        <v>3.00074018181229</v>
       </c>
       <c r="E5">
-        <v>2.177960719701232</v>
+        <v>-2.84961395106605</v>
       </c>
       <c r="F5">
-        <v>0.007202834809093631</v>
+        <v>0.1511262307462402</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6069</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>6833</v>
       </c>
       <c r="D6">
-        <v>-13.62585884460771</v>
+        <v>-7.328930960304077</v>
       </c>
       <c r="E6">
-        <v>13.81101796380883</v>
+        <v>7.333157194120574</v>
       </c>
       <c r="F6">
-        <v>0.1851591192011171</v>
+        <v>0.004226233816496949</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>6069</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>2268</v>
       </c>
       <c r="D7">
-        <v>-16.17622179390136</v>
+        <v>44.42252201540236</v>
       </c>
       <c r="E7">
-        <v>16.27283349831609</v>
+        <v>-44.39336191920118</v>
       </c>
       <c r="F7">
-        <v>0.09661170441473133</v>
+        <v>0.0291600962011751</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6069</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>7180</v>
       </c>
       <c r="D8">
-        <v>39.99061092126085</v>
+        <v>-6.336800532636929</v>
       </c>
       <c r="E8">
-        <v>-39.56683373373679</v>
+        <v>6.337028440743059</v>
       </c>
       <c r="F8">
-        <v>0.4237771875240715</v>
+        <v>0.0002279081061304367</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6069</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>6293</v>
       </c>
       <c r="D9">
-        <v>26.79852487197217</v>
+        <v>-8.657049570922808</v>
       </c>
       <c r="E9">
-        <v>-26.55531476502497</v>
+        <v>8.658104555619495</v>
       </c>
       <c r="F9">
-        <v>0.2432101069471948</v>
+        <v>0.001054984696685635</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>1968</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>9192</v>
       </c>
       <c r="D10">
-        <v>60.48371497749191</v>
+        <v>-1.028818787544245</v>
       </c>
       <c r="E10">
-        <v>-60.00271306305106</v>
+        <v>1.029238840863863</v>
       </c>
       <c r="F10">
-        <v>0.4810019144408484</v>
+        <v>0.0004200533196184464</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>1968</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>3493</v>
       </c>
       <c r="D11">
-        <v>0.8666325320490833</v>
+        <v>0.1143666238139598</v>
       </c>
       <c r="E11">
-        <v>-0.828132592992624</v>
+        <v>-0.1137344772735425</v>
       </c>
       <c r="F11">
-        <v>0.03849993905645933</v>
+        <v>0.000632146540417342</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>1968</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>955</v>
       </c>
       <c r="D12">
-        <v>59.27879633480803</v>
+        <v>-6.075342876511377</v>
       </c>
       <c r="E12">
-        <v>-57.79375249211599</v>
+        <v>6.158288933429072</v>
       </c>
       <c r="F12">
-        <v>1.485043842692035</v>
+        <v>0.08294605691769458</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>1968</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="D13">
-        <v>41.8748633345406</v>
+        <v>0.1303212942049143</v>
       </c>
       <c r="E13">
-        <v>-41.1063102571603</v>
+        <v>-0.1297089000634509</v>
       </c>
       <c r="F13">
-        <v>0.7685530773803018</v>
+        <v>0.0006123941414634638</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>1968</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>6826</v>
       </c>
       <c r="D14">
-        <v>109.6011981598082</v>
+        <v>8.330163145461489</v>
       </c>
       <c r="E14">
-        <v>-108.8520696999671</v>
+        <v>-8.312085082326718</v>
       </c>
       <c r="F14">
-        <v>0.7491284598411196</v>
+        <v>0.01807806313477156</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>1968</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>8964</v>
       </c>
       <c r="D15">
-        <v>88.67183392873311</v>
+        <v>0.2844422246468371</v>
       </c>
       <c r="E15">
-        <v>-88.17328637669706</v>
+        <v>-0.280371971388526</v>
       </c>
       <c r="F15">
-        <v>0.4985475520360438</v>
+        <v>0.004070253258311052</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>1968</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>5776</v>
       </c>
       <c r="D16">
-        <v>101.7894053193537</v>
+        <v>0.3772955998084254</v>
       </c>
       <c r="E16">
-        <v>-101.1536177450771</v>
+        <v>-0.376256199681842</v>
       </c>
       <c r="F16">
-        <v>0.635787574276625</v>
+        <v>0.001039400126583373</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="B17">
-        <v>12</v>
+        <v>9192</v>
       </c>
       <c r="C17">
-        <v>23</v>
+        <v>955</v>
       </c>
       <c r="D17">
-        <v>106.5771639652878</v>
+        <v>-1.176540053398667</v>
       </c>
       <c r="E17">
-        <v>-105.1150167894688</v>
+        <v>1.193335908146423</v>
       </c>
       <c r="F17">
-        <v>1.462147175819006</v>
+        <v>0.01679585474775609</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="B18">
-        <v>13</v>
+        <v>9192</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>6826</v>
       </c>
       <c r="D18">
-        <v>64.12976855615607</v>
+        <v>1.303512504415539</v>
       </c>
       <c r="E18">
-        <v>-63.60959296241284</v>
+        <v>-1.30059653268288</v>
       </c>
       <c r="F18">
-        <v>0.5201755937432218</v>
+        <v>0.002915971732659652</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>9192</v>
       </c>
       <c r="C19">
-        <v>16</v>
+        <v>8964</v>
       </c>
       <c r="D19">
-        <v>138.2004012579186</v>
+        <v>0.3389013809024433</v>
       </c>
       <c r="E19">
-        <v>-137.2154395946111</v>
+        <v>-0.3374635288694945</v>
       </c>
       <c r="F19">
-        <v>0.984961663307482</v>
+        <v>0.001437852032948718</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>8574</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>1616</v>
       </c>
       <c r="D20">
-        <v>-33.78791740353954</v>
+        <v>9.067302028386852</v>
       </c>
       <c r="E20">
-        <v>33.81442658588467</v>
+        <v>-9.066917278386622</v>
       </c>
       <c r="F20">
-        <v>0.02650918234513022</v>
+        <v>0.0003847500002304716</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>8574</v>
       </c>
       <c r="C21">
-        <v>21</v>
+        <v>1163</v>
       </c>
       <c r="D21">
-        <v>59.3871837666554</v>
+        <v>-15.9103482611983</v>
       </c>
       <c r="E21">
-        <v>-59.15908243433773</v>
+        <v>15.91319586644131</v>
       </c>
       <c r="F21">
-        <v>0.2281013323176651</v>
+        <v>0.002847605243017082</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>8574</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>9064</v>
       </c>
       <c r="D22">
-        <v>59.3871837666554</v>
+        <v>7.780446315093689</v>
       </c>
       <c r="E22">
-        <v>-59.15908243433773</v>
+        <v>-7.780151744019618</v>
       </c>
       <c r="F22">
-        <v>0.2281013323176651</v>
+        <v>0.0002945710740706597</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>8574</v>
       </c>
       <c r="C23">
-        <v>24</v>
+        <v>8921</v>
       </c>
       <c r="D23">
-        <v>-102.7759528167307</v>
+        <v>23.8972806209313</v>
       </c>
       <c r="E23">
-        <v>103.5157424969224</v>
+        <v>-23.89532327353446</v>
       </c>
       <c r="F23">
-        <v>0.7397896801916826</v>
+        <v>0.001957347396841502</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>3493</v>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>2299</v>
       </c>
       <c r="D24">
-        <v>93.66218532542231</v>
+        <v>-0.1536221025930902</v>
       </c>
       <c r="E24">
-        <v>-93.35961086188355</v>
+        <v>0.1541925217960542</v>
       </c>
       <c r="F24">
-        <v>0.3025744635387628</v>
+        <v>0.0005704192029640492</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>2299</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>4423</v>
       </c>
       <c r="D25">
-        <v>-6.54267629861722</v>
+        <v>7.500141062074905</v>
       </c>
       <c r="E25">
-        <v>6.544304880753604</v>
+        <v>-7.500141062074905</v>
       </c>
       <c r="F25">
-        <v>0.001628582136384282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="B26">
-        <v>17</v>
+        <v>6826</v>
       </c>
       <c r="C26">
-        <v>18</v>
+        <v>2299</v>
       </c>
       <c r="D26">
-        <v>64.10686999533122</v>
+        <v>-0.01503805525821649</v>
       </c>
       <c r="E26">
-        <v>-64.03069668473964</v>
+        <v>0.01510866212655732</v>
       </c>
       <c r="F26">
-        <v>0.07617331059158738</v>
+        <v>7.060686834083562E-05</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="B27">
-        <v>17</v>
+        <v>7563</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>2299</v>
       </c>
       <c r="D27">
-        <v>29.76212273692076</v>
+        <v>1.180181284048645</v>
       </c>
       <c r="E27">
-        <v>-29.63148864068269</v>
+        <v>-1.176508687932569</v>
       </c>
       <c r="F27">
-        <v>0.1306340962380748</v>
+        <v>0.003672596116075996</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>4427</v>
       </c>
       <c r="C28">
-        <v>21</v>
+        <v>2299</v>
       </c>
       <c r="D28">
-        <v>5.683372288646154</v>
+        <v>2.155307235611877</v>
       </c>
       <c r="E28">
-        <v>-5.68162066644945</v>
+        <v>-2.152464419757631</v>
       </c>
       <c r="F28">
-        <v>0.001751622196704411</v>
+        <v>0.002842815854245048</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>8335</v>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>2299</v>
       </c>
       <c r="D29">
-        <v>5.683372288646154</v>
+        <v>0.3175440790321846</v>
       </c>
       <c r="E29">
-        <v>-5.68162066644945</v>
+        <v>-0.3122694952766813</v>
       </c>
       <c r="F29">
-        <v>0.001751622196704411</v>
+        <v>0.005274583755503302</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="B30">
-        <v>19</v>
+        <v>5155</v>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>2299</v>
       </c>
       <c r="D30">
-        <v>18.56936008705726</v>
+        <v>0.6929313871469122</v>
       </c>
       <c r="E30">
-        <v>-18.55125074332018</v>
+        <v>-0.6925839253455296</v>
       </c>
       <c r="F30">
-        <v>0.0181093437370744</v>
+        <v>0.0003474618013825717</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="B31">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>2299</v>
       </c>
       <c r="D31">
-        <v>18.56936008705726</v>
+        <v>9.442996554071978</v>
       </c>
       <c r="E31">
-        <v>-18.55125074332018</v>
+        <v>-9.418232022323048</v>
       </c>
       <c r="F31">
-        <v>0.0181093437370744</v>
+        <v>0.02476453174893034</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>2449</v>
       </c>
       <c r="C32">
-        <v>23</v>
+        <v>2299</v>
       </c>
       <c r="D32">
-        <v>38.94653203930537</v>
+        <v>0.1605128422597364</v>
       </c>
       <c r="E32">
-        <v>-38.90296859826503</v>
+        <v>-0.1598086218871716</v>
       </c>
       <c r="F32">
-        <v>0.04356344104034515</v>
+        <v>0.0007042203725647319</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="B33">
-        <v>20</v>
+        <v>4665</v>
       </c>
       <c r="C33">
-        <v>23</v>
+        <v>2299</v>
       </c>
       <c r="D33">
-        <v>38.94653203930537</v>
+        <v>7.055190547108996</v>
       </c>
       <c r="E33">
-        <v>-38.90296859826503</v>
+        <v>-7.047436452600555</v>
       </c>
       <c r="F33">
-        <v>0.04356344104034515</v>
+        <v>0.007754094508441445</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="B34">
-        <v>21</v>
+        <v>4495</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>2299</v>
       </c>
       <c r="D34">
-        <v>30.23787126379522</v>
+        <v>0.4385645170403588</v>
       </c>
       <c r="E34">
-        <v>-30.14111311059066</v>
+        <v>-0.4383824846044256</v>
       </c>
       <c r="F34">
-        <v>0.09675815320456804</v>
+        <v>0.0001820324359331528</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35">
+        <v>3493</v>
+      </c>
+      <c r="C35">
+        <v>5587</v>
+      </c>
+      <c r="D35">
+        <v>10.09672568897215</v>
+      </c>
+      <c r="E35">
+        <v>-10.09672568897215</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36">
+        <v>4586</v>
+      </c>
+      <c r="C36">
+        <v>3493</v>
+      </c>
+      <c r="D36">
+        <v>-1.145135052810338</v>
+      </c>
+      <c r="E36">
+        <v>1.145287636378517</v>
+      </c>
+      <c r="F36">
+        <v>0.0001525835681789878</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37">
+        <v>228</v>
+      </c>
+      <c r="C37">
+        <v>3493</v>
+      </c>
+      <c r="D37">
+        <v>-1.449950100444888</v>
+      </c>
+      <c r="E37">
+        <v>1.450774280246295</v>
+      </c>
+      <c r="F37">
+        <v>0.0008241798014060192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38">
+        <v>6826</v>
+      </c>
+      <c r="C38">
+        <v>3493</v>
+      </c>
+      <c r="D38">
+        <v>-0.1746114235452928</v>
+      </c>
+      <c r="E38">
+        <v>0.1769698613133937</v>
+      </c>
+      <c r="F38">
+        <v>0.002358437768100897</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39">
+        <v>7563</v>
+      </c>
+      <c r="C39">
+        <v>3493</v>
+      </c>
+      <c r="D39">
+        <v>0.6563273973037467</v>
+      </c>
+      <c r="E39">
+        <v>-0.6543568960058852</v>
+      </c>
+      <c r="F39">
+        <v>0.001970501297861478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40">
+        <v>4427</v>
+      </c>
+      <c r="C40">
+        <v>3493</v>
+      </c>
+      <c r="D40">
+        <v>1.919920452244032</v>
+      </c>
+      <c r="E40">
+        <v>-1.913519005900648</v>
+      </c>
+      <c r="F40">
+        <v>0.006401446343384451</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41">
+        <v>8335</v>
+      </c>
+      <c r="C41">
+        <v>3493</v>
+      </c>
+      <c r="D41">
+        <v>0.2703553018566123</v>
+      </c>
+      <c r="E41">
+        <v>-0.266706396626481</v>
+      </c>
+      <c r="F41">
+        <v>0.003648905230131195</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42">
+        <v>5155</v>
+      </c>
+      <c r="C42">
+        <v>3493</v>
+      </c>
+      <c r="D42">
+        <v>7.927866596497664</v>
+      </c>
+      <c r="E42">
+        <v>-7.905719614197078</v>
+      </c>
+      <c r="F42">
+        <v>0.02214698230058598</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43">
+        <v>271</v>
+      </c>
+      <c r="C43">
+        <v>3493</v>
+      </c>
+      <c r="D43">
+        <v>0.4345521103007464</v>
+      </c>
+      <c r="E43">
+        <v>-0.4343239887783732</v>
+      </c>
+      <c r="F43">
+        <v>0.0002281215223731009</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44">
+        <v>5776</v>
+      </c>
+      <c r="C44">
+        <v>3493</v>
+      </c>
+      <c r="D44">
+        <v>-0.08932549435777611</v>
+      </c>
+      <c r="E44">
+        <v>0.09078929352638929</v>
+      </c>
+      <c r="F44">
+        <v>0.001463799168613183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45">
+        <v>2449</v>
+      </c>
+      <c r="C45">
+        <v>3493</v>
+      </c>
+      <c r="D45">
+        <v>0.1255452499885046</v>
+      </c>
+      <c r="E45">
+        <v>-0.1252307307355139</v>
+      </c>
+      <c r="F45">
+        <v>0.0003145192529906268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46">
+        <v>4665</v>
+      </c>
+      <c r="C46">
+        <v>3493</v>
+      </c>
+      <c r="D46">
+        <v>0.1892693899474603</v>
+      </c>
+      <c r="E46">
+        <v>-0.1891035842296891</v>
+      </c>
+      <c r="F46">
+        <v>0.0001658057177712086</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47">
+        <v>4495</v>
+      </c>
+      <c r="C47">
+        <v>3493</v>
+      </c>
+      <c r="D47">
+        <v>3.06595590973229</v>
+      </c>
+      <c r="E47">
+        <v>-3.06139319749665</v>
+      </c>
+      <c r="F47">
+        <v>0.004562712235640226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>170</v>
+      </c>
+      <c r="B48">
+        <v>5587</v>
+      </c>
+      <c r="C48">
+        <v>4586</v>
+      </c>
+      <c r="D48">
+        <v>20.63599273244276</v>
+      </c>
+      <c r="E48">
+        <v>-20.61769290533345</v>
+      </c>
+      <c r="F48">
+        <v>0.018299827109311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>171</v>
+      </c>
+      <c r="B49">
+        <v>4423</v>
+      </c>
+      <c r="C49">
+        <v>4586</v>
+      </c>
+      <c r="D49">
+        <v>20.23567961221362</v>
+      </c>
+      <c r="E49">
+        <v>-20.22258712791338</v>
+      </c>
+      <c r="F49">
+        <v>0.01309248430023391</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50">
+        <v>4929</v>
+      </c>
+      <c r="C50">
+        <v>2870</v>
+      </c>
+      <c r="D50">
+        <v>-10.26373097446955</v>
+      </c>
+      <c r="E50">
+        <v>10.26382158127621</v>
+      </c>
+      <c r="F50">
+        <v>9.060680666167498E-05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>173</v>
+      </c>
+      <c r="B51">
+        <v>4929</v>
+      </c>
+      <c r="C51">
+        <v>659</v>
+      </c>
+      <c r="D51">
+        <v>37.43666455944454</v>
+      </c>
+      <c r="E51">
+        <v>-37.42245753435837</v>
+      </c>
+      <c r="F51">
+        <v>0.01420702508617144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52">
+        <v>4929</v>
+      </c>
+      <c r="C52">
+        <v>1037</v>
+      </c>
+      <c r="D52">
+        <v>-10.26352800628802</v>
+      </c>
+      <c r="E52">
+        <v>10.26361877865398</v>
+      </c>
+      <c r="F52">
+        <v>9.077236595989024E-05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B53">
+        <v>4929</v>
+      </c>
+      <c r="C53">
+        <v>659</v>
+      </c>
+      <c r="D53">
+        <v>43.90519753707951</v>
+      </c>
+      <c r="E53">
+        <v>-43.88381648271261</v>
+      </c>
+      <c r="F53">
+        <v>0.02138105436689797</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54">
+        <v>1815</v>
+      </c>
+      <c r="C54">
+        <v>5210</v>
+      </c>
+      <c r="D54">
+        <v>-0.05854020981573068</v>
+      </c>
+      <c r="E54">
+        <v>0.06215913273437014</v>
+      </c>
+      <c r="F54">
+        <v>0.003618922918639464</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55">
+        <v>1815</v>
+      </c>
+      <c r="C55">
+        <v>1445</v>
+      </c>
+      <c r="D55">
+        <v>0.9115746330386691</v>
+      </c>
+      <c r="E55">
+        <v>-0.8403281321634232</v>
+      </c>
+      <c r="F55">
+        <v>0.07124650087524595</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56">
+        <v>1616</v>
+      </c>
+      <c r="C56">
+        <v>7762</v>
+      </c>
+      <c r="D56">
+        <v>39.96839787277359</v>
+      </c>
+      <c r="E56">
+        <v>-39.96019029881986</v>
+      </c>
+      <c r="F56">
+        <v>0.008207573953733505</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57">
+        <v>1616</v>
+      </c>
+      <c r="C57">
+        <v>2520</v>
+      </c>
+      <c r="D57">
+        <v>-11.5017820757746</v>
+      </c>
+      <c r="E57">
+        <v>11.50251975880226</v>
+      </c>
+      <c r="F57">
+        <v>0.0007376830276559221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58">
+        <v>9064</v>
+      </c>
+      <c r="C58">
+        <v>7762</v>
+      </c>
+      <c r="D58">
+        <v>39.13574669863912</v>
+      </c>
+      <c r="E58">
+        <v>-39.13033117080933</v>
+      </c>
+      <c r="F58">
+        <v>0.005415527829788491</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59">
+        <v>9064</v>
+      </c>
+      <c r="C59">
+        <v>89</v>
+      </c>
+      <c r="D59">
+        <v>-11.35983868109577</v>
+      </c>
+      <c r="E59">
+        <v>11.36110562420697</v>
+      </c>
+      <c r="F59">
+        <v>0.001266943111198626</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60">
+        <v>1317</v>
+      </c>
+      <c r="C60">
+        <v>659</v>
+      </c>
+      <c r="D60">
+        <v>29.18010274442249</v>
+      </c>
+      <c r="E60">
+        <v>-29.17313344775784</v>
+      </c>
+      <c r="F60">
+        <v>0.006969296664643965</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61">
+        <v>1317</v>
+      </c>
+      <c r="C61">
+        <v>8605</v>
+      </c>
+      <c r="D61">
+        <v>67.20066440224772</v>
+      </c>
+      <c r="E61">
+        <v>-67.1515509740377</v>
+      </c>
+      <c r="F61">
+        <v>0.04911342821001252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62">
+        <v>8605</v>
+      </c>
+      <c r="C62">
+        <v>1367</v>
+      </c>
+      <c r="D62">
+        <v>-79.6049240005747</v>
+      </c>
+      <c r="E62">
+        <v>79.60787730045158</v>
+      </c>
+      <c r="F62">
+        <v>0.002953299876884419</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63">
+        <v>8605</v>
+      </c>
+      <c r="C63">
+        <v>8921</v>
+      </c>
+      <c r="D63">
+        <v>-85.04245487313788</v>
+      </c>
+      <c r="E63">
+        <v>85.1082761368851</v>
+      </c>
+      <c r="F63">
+        <v>0.0658212637472122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64">
+        <v>1163</v>
+      </c>
+      <c r="C64">
+        <v>1676</v>
+      </c>
+      <c r="D64">
+        <v>-4.302826174775485</v>
+      </c>
+      <c r="E64">
+        <v>4.302837938339111</v>
+      </c>
+      <c r="F64">
+        <v>1.176356362597719E-05</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65">
+        <v>1163</v>
+      </c>
+      <c r="C65">
+        <v>7051</v>
+      </c>
+      <c r="D65">
+        <v>0.05021682390409481</v>
+      </c>
+      <c r="E65">
+        <v>-0.05021592620687842</v>
+      </c>
+      <c r="F65">
+        <v>8.976972163884933E-07</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66">
+        <v>913</v>
+      </c>
+      <c r="C66">
+        <v>7762</v>
+      </c>
+      <c r="D66">
+        <v>-146.0341438437495</v>
+      </c>
+      <c r="E66">
+        <v>146.151038290637</v>
+      </c>
+      <c r="F66">
+        <v>0.1168944468874056</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67">
+        <v>2107</v>
+      </c>
+      <c r="C67">
+        <v>7762</v>
+      </c>
+      <c r="D67">
+        <v>-140.850131619052</v>
+      </c>
+      <c r="E67">
+        <v>140.9565903939277</v>
+      </c>
+      <c r="F67">
+        <v>0.1064587748757395</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68">
+        <v>2107</v>
+      </c>
+      <c r="C68">
+        <v>5996</v>
+      </c>
+      <c r="D68">
+        <v>-132.5539590155389</v>
+      </c>
+      <c r="E68">
+        <v>132.5867195822713</v>
+      </c>
+      <c r="F68">
+        <v>0.03276056673233718</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69">
+        <v>2107</v>
+      </c>
+      <c r="C69">
+        <v>6293</v>
+      </c>
+      <c r="D69">
+        <v>-124.9052066416309</v>
+      </c>
+      <c r="E69">
+        <v>125.2083879234675</v>
+      </c>
+      <c r="F69">
+        <v>0.3031812818366397</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70">
+        <v>913</v>
+      </c>
+      <c r="C70">
+        <v>7762</v>
+      </c>
+      <c r="D70">
+        <v>-153.2527854999832</v>
+      </c>
+      <c r="E70">
+        <v>153.3925203971937</v>
+      </c>
+      <c r="F70">
+        <v>0.1397348972104862</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>193</v>
+      </c>
+      <c r="B71">
+        <v>6704</v>
+      </c>
+      <c r="C71">
+        <v>8921</v>
+      </c>
+      <c r="D71">
+        <v>15.89680290597908</v>
+      </c>
+      <c r="E71">
+        <v>-15.89602440090201</v>
+      </c>
+      <c r="F71">
+        <v>0.000778505077070335</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72">
+        <v>228</v>
+      </c>
+      <c r="C72">
+        <v>4586</v>
+      </c>
+      <c r="D72">
+        <v>13.18126653883722</v>
+      </c>
+      <c r="E72">
+        <v>-13.17208488232974</v>
+      </c>
+      <c r="F72">
+        <v>0.009181656507481484</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73">
+        <v>2441</v>
+      </c>
+      <c r="C73">
+        <v>6293</v>
+      </c>
+      <c r="D73">
+        <v>31.2418685799174</v>
+      </c>
+      <c r="E73">
+        <v>-31.23909829324352</v>
+      </c>
+      <c r="F73">
+        <v>0.002770286673881017</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74">
+        <v>955</v>
+      </c>
+      <c r="C74">
+        <v>3506</v>
+      </c>
+      <c r="D74">
+        <v>-1.192416148493659</v>
+      </c>
+      <c r="E74">
+        <v>1.192416148493659</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75">
+        <v>955</v>
+      </c>
+      <c r="C75">
+        <v>8964</v>
+      </c>
+      <c r="D75">
+        <v>4.936703225688606</v>
+      </c>
+      <c r="E75">
+        <v>-4.864313115177313</v>
+      </c>
+      <c r="F75">
+        <v>0.07239011051129243</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>198</v>
+      </c>
+      <c r="B76">
+        <v>3506</v>
+      </c>
+      <c r="C76">
+        <v>2908</v>
+      </c>
+      <c r="D76">
+        <v>5.491286902725726</v>
+      </c>
+      <c r="E76">
+        <v>-5.482444991331564</v>
+      </c>
+      <c r="F76">
+        <v>0.008841911394162627</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77">
+        <v>228</v>
+      </c>
+      <c r="C77">
+        <v>6826</v>
+      </c>
+      <c r="D77">
+        <v>0.03278691027403498</v>
+      </c>
+      <c r="E77">
+        <v>-0.03092631858994964</v>
+      </c>
+      <c r="F77">
+        <v>0.001860591684085339</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>200</v>
+      </c>
+      <c r="B78">
+        <v>228</v>
+      </c>
+      <c r="C78">
+        <v>5776</v>
+      </c>
+      <c r="D78">
+        <v>0.04950672261636083</v>
+      </c>
+      <c r="E78">
+        <v>-0.04824555524290085</v>
+      </c>
+      <c r="F78">
+        <v>0.001261167373459979</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79">
+        <v>8964</v>
+      </c>
+      <c r="C79">
+        <v>6826</v>
+      </c>
+      <c r="D79">
+        <v>1.434021495280611</v>
+      </c>
+      <c r="E79">
+        <v>-1.428200696019651</v>
+      </c>
+      <c r="F79">
+        <v>0.005820799260959977</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>202</v>
+      </c>
+      <c r="B80">
+        <v>5776</v>
+      </c>
+      <c r="C80">
+        <v>6826</v>
+      </c>
+      <c r="D80">
+        <v>0.7706900980582918</v>
+      </c>
+      <c r="E80">
+        <v>-0.7692775723973572</v>
+      </c>
+      <c r="F80">
+        <v>0.0014125256609346</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81">
+        <v>659</v>
+      </c>
+      <c r="C81">
+        <v>8329</v>
+      </c>
+      <c r="D81">
+        <v>-50.72640267730881</v>
+      </c>
+      <c r="E81">
+        <v>50.73723926668517</v>
+      </c>
+      <c r="F81">
+        <v>0.01083658937636178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82">
+        <v>659</v>
+      </c>
+      <c r="C82">
+        <v>7051</v>
+      </c>
+      <c r="D82">
+        <v>-30.96780624735525</v>
+      </c>
+      <c r="E82">
+        <v>30.9823464321721</v>
+      </c>
+      <c r="F82">
+        <v>0.01454018481685249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B83">
+        <v>659</v>
+      </c>
+      <c r="C83">
+        <v>9239</v>
+      </c>
+      <c r="D83">
+        <v>84.55657548220414</v>
+      </c>
+      <c r="E83">
+        <v>-84.55156405400488</v>
+      </c>
+      <c r="F83">
+        <v>0.005011428199253043</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84">
+        <v>659</v>
+      </c>
+      <c r="C84">
+        <v>7960</v>
+      </c>
+      <c r="D84">
+        <v>84.55658188831457</v>
+      </c>
+      <c r="E84">
+        <v>-84.55157046584229</v>
+      </c>
+      <c r="F84">
+        <v>0.005011422472278593</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85">
+        <v>659</v>
+      </c>
+      <c r="C85">
+        <v>6233</v>
+      </c>
+      <c r="D85">
+        <v>124.5506603173293</v>
+      </c>
+      <c r="E85">
+        <v>-124.5398257208723</v>
+      </c>
+      <c r="F85">
+        <v>0.01083459645705442</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86">
+        <v>659</v>
+      </c>
+      <c r="C86">
+        <v>5416</v>
+      </c>
+      <c r="D86">
+        <v>-10.36657558138856</v>
+      </c>
+      <c r="E86">
+        <v>10.36843629001118</v>
+      </c>
+      <c r="F86">
+        <v>0.001860708622609952</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87">
+        <v>659</v>
+      </c>
+      <c r="C87">
+        <v>6798</v>
+      </c>
+      <c r="D87">
+        <v>117.8448576543987</v>
+      </c>
+      <c r="E87">
+        <v>-117.8335379366914</v>
+      </c>
+      <c r="F87">
+        <v>0.01131971770729212</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>210</v>
+      </c>
+      <c r="B88">
+        <v>792</v>
+      </c>
+      <c r="C88">
+        <v>3279</v>
+      </c>
+      <c r="D88">
+        <v>3.131130155822649</v>
+      </c>
+      <c r="E88">
+        <v>-3.131130155822649</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89">
+        <v>7563</v>
+      </c>
+      <c r="C89">
+        <v>792</v>
+      </c>
+      <c r="D89">
+        <v>-0.1532312008452789</v>
+      </c>
+      <c r="E89">
+        <v>0.1587446700377772</v>
+      </c>
+      <c r="F89">
+        <v>0.005513469192498311</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90">
+        <v>7279</v>
+      </c>
+      <c r="C90">
+        <v>792</v>
+      </c>
+      <c r="D90">
+        <v>-3.190113897257838</v>
+      </c>
+      <c r="E90">
+        <v>3.2660234357312</v>
+      </c>
+      <c r="F90">
+        <v>0.07590953847336143</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>213</v>
+      </c>
+      <c r="B91">
+        <v>8335</v>
+      </c>
+      <c r="C91">
+        <v>792</v>
+      </c>
+      <c r="D91">
+        <v>-8.351011238429765</v>
+      </c>
+      <c r="E91">
+        <v>8.410887552465478</v>
+      </c>
+      <c r="F91">
+        <v>0.05987631403571447</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92">
+        <v>2449</v>
+      </c>
+      <c r="C92">
+        <v>792</v>
+      </c>
+      <c r="D92">
+        <v>-3.802204489977854</v>
+      </c>
+      <c r="E92">
+        <v>3.869574579380763</v>
+      </c>
+      <c r="F92">
+        <v>0.06737008940290862</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93">
+        <v>4665</v>
+      </c>
+      <c r="C93">
+        <v>792</v>
+      </c>
+      <c r="D93">
+        <v>-1.032388147935556</v>
+      </c>
+      <c r="E93">
+        <v>1.058861086868069</v>
+      </c>
+      <c r="F93">
+        <v>0.02647293893251294</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94">
+        <v>4495</v>
+      </c>
+      <c r="C94">
+        <v>792</v>
+      </c>
+      <c r="D94">
+        <v>-0.8849120165627302</v>
+      </c>
+      <c r="E94">
+        <v>0.9046507432086983</v>
+      </c>
+      <c r="F94">
+        <v>0.0197387266459681</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>217</v>
+      </c>
+      <c r="B95">
+        <v>5416</v>
+      </c>
+      <c r="C95">
+        <v>2267</v>
+      </c>
+      <c r="D95">
+        <v>80.02234994195797</v>
+      </c>
+      <c r="E95">
+        <v>-80.00434787035744</v>
+      </c>
+      <c r="F95">
+        <v>0.01800207160054246</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96">
+        <v>5416</v>
+      </c>
+      <c r="C96">
+        <v>7637</v>
+      </c>
+      <c r="D96">
+        <v>-23.07359977193954</v>
+      </c>
+      <c r="E96">
+        <v>23.07970277003497</v>
+      </c>
+      <c r="F96">
+        <v>0.006102998095428025</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97">
+        <v>8964</v>
+      </c>
+      <c r="C97">
+        <v>2168</v>
+      </c>
+      <c r="D97">
+        <v>0.744070680270434</v>
+      </c>
+      <c r="E97">
+        <v>-0.744070680270434</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98">
+        <v>3659</v>
+      </c>
+      <c r="C98">
+        <v>5996</v>
+      </c>
+      <c r="D98">
+        <v>-162.8790586629173</v>
+      </c>
+      <c r="E98">
+        <v>162.9347067424471</v>
+      </c>
+      <c r="F98">
+        <v>0.05564807952984641</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99">
+        <v>5762</v>
+      </c>
+      <c r="C99">
+        <v>5996</v>
+      </c>
+      <c r="D99">
+        <v>38.02296743908023</v>
+      </c>
+      <c r="E99">
+        <v>-38.01991965726434</v>
+      </c>
+      <c r="F99">
+        <v>0.003047781815890271</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100">
+        <v>3242</v>
+      </c>
+      <c r="C100">
+        <v>5097</v>
+      </c>
+      <c r="D100">
+        <v>-26.30011963922016</v>
+      </c>
+      <c r="E100">
+        <v>26.30011963922016</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101">
+        <v>7563</v>
+      </c>
+      <c r="C101">
+        <v>3242</v>
+      </c>
+      <c r="D101">
+        <v>-27.49984630364627</v>
+      </c>
+      <c r="E101">
+        <v>27.70838803478927</v>
+      </c>
+      <c r="F101">
+        <v>0.2085417311430082</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>224</v>
+      </c>
+      <c r="B102">
+        <v>4427</v>
+      </c>
+      <c r="C102">
+        <v>3242</v>
+      </c>
+      <c r="D102">
+        <v>-0.4889834566670146</v>
+      </c>
+      <c r="E102">
+        <v>0.4909504386574667</v>
+      </c>
+      <c r="F102">
+        <v>0.001966981990452095</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>225</v>
+      </c>
+      <c r="B103">
+        <v>3242</v>
+      </c>
+      <c r="C103">
+        <v>7279</v>
+      </c>
+      <c r="D103">
+        <v>43.06161249175106</v>
+      </c>
+      <c r="E103">
+        <v>-42.84245216049853</v>
+      </c>
+      <c r="F103">
+        <v>0.2191603312525325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104">
+        <v>271</v>
+      </c>
+      <c r="C104">
+        <v>3242</v>
+      </c>
+      <c r="D104">
+        <v>-0.4053704042792047</v>
+      </c>
+      <c r="E104">
+        <v>0.4056059249872478</v>
+      </c>
+      <c r="F104">
+        <v>0.000235520708043082</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105">
+        <v>3242</v>
+      </c>
+      <c r="C105">
+        <v>1611</v>
+      </c>
+      <c r="D105">
+        <v>2.661187307815753</v>
+      </c>
+      <c r="E105">
+        <v>-2.655064220269943</v>
+      </c>
+      <c r="F105">
+        <v>0.00612308754580973</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106">
+        <v>5097</v>
+      </c>
+      <c r="C106">
+        <v>1611</v>
+      </c>
+      <c r="D106">
+        <v>57.52945543631937</v>
+      </c>
+      <c r="E106">
+        <v>-57.382755185513</v>
+      </c>
+      <c r="F106">
+        <v>0.1467002508063753</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107">
+        <v>8181</v>
+      </c>
+      <c r="C107">
+        <v>8179</v>
+      </c>
+      <c r="D107">
+        <v>-13.93570706862959</v>
+      </c>
+      <c r="E107">
+        <v>13.93660723067401</v>
+      </c>
+      <c r="F107">
+        <v>0.0009001620444148983</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>230</v>
+      </c>
+      <c r="B108">
+        <v>8181</v>
+      </c>
+      <c r="C108">
+        <v>7762</v>
+      </c>
+      <c r="D108">
+        <v>48.23766604546785</v>
+      </c>
+      <c r="E108">
+        <v>-48.22590837862735</v>
+      </c>
+      <c r="F108">
+        <v>0.01175766684050061</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>231</v>
+      </c>
+      <c r="B109">
+        <v>9025</v>
+      </c>
+      <c r="C109">
+        <v>7762</v>
+      </c>
+      <c r="D109">
+        <v>42.93774367074643</v>
+      </c>
+      <c r="E109">
+        <v>-42.92861139290925</v>
+      </c>
+      <c r="F109">
+        <v>0.009132277837176073</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>232</v>
+      </c>
+      <c r="B110">
+        <v>7563</v>
+      </c>
+      <c r="C110">
+        <v>4427</v>
+      </c>
+      <c r="D110">
+        <v>1.094654453597274</v>
+      </c>
+      <c r="E110">
+        <v>-1.093083874554049</v>
+      </c>
+      <c r="F110">
+        <v>0.001570579043225218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>233</v>
+      </c>
+      <c r="B111">
+        <v>7563</v>
+      </c>
+      <c r="C111">
+        <v>7279</v>
+      </c>
+      <c r="D111">
+        <v>8.428134043618767</v>
+      </c>
+      <c r="E111">
+        <v>-8.396804369161272</v>
+      </c>
+      <c r="F111">
+        <v>0.03132967445749479</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112">
+        <v>7563</v>
+      </c>
+      <c r="C112">
+        <v>8335</v>
+      </c>
+      <c r="D112">
+        <v>0.5340177069919055</v>
+      </c>
+      <c r="E112">
+        <v>-0.524856530442998</v>
+      </c>
+      <c r="F112">
+        <v>0.00916117654890759</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113">
+        <v>7563</v>
+      </c>
+      <c r="C113">
+        <v>5155</v>
+      </c>
+      <c r="D113">
+        <v>0.4058397643838576</v>
+      </c>
+      <c r="E113">
+        <v>-0.4057593888438161</v>
+      </c>
+      <c r="F113">
+        <v>8.037554004147046E-05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>236</v>
+      </c>
+      <c r="B114">
+        <v>7563</v>
+      </c>
+      <c r="C114">
+        <v>271</v>
+      </c>
+      <c r="D114">
+        <v>0.5238945315709075</v>
+      </c>
+      <c r="E114">
+        <v>-0.5238269746476417</v>
+      </c>
+      <c r="F114">
+        <v>6.755692326569987E-05</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>237</v>
+      </c>
+      <c r="B115">
+        <v>2449</v>
+      </c>
+      <c r="C115">
+        <v>7563</v>
+      </c>
+      <c r="D115">
+        <v>-0.1226115481309269</v>
+      </c>
+      <c r="E115">
+        <v>0.1229305026790823</v>
+      </c>
+      <c r="F115">
+        <v>0.0003189545481553603</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>238</v>
+      </c>
+      <c r="B116">
+        <v>4665</v>
+      </c>
+      <c r="C116">
+        <v>7563</v>
+      </c>
+      <c r="D116">
+        <v>-16.81242054192349</v>
+      </c>
+      <c r="E116">
+        <v>16.846063960783</v>
+      </c>
+      <c r="F116">
+        <v>0.03364341885951638</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B117">
+        <v>4495</v>
+      </c>
+      <c r="C117">
+        <v>7563</v>
+      </c>
+      <c r="D117">
+        <v>-0.5988981514927895</v>
+      </c>
+      <c r="E117">
+        <v>0.6012967319853999</v>
+      </c>
+      <c r="F117">
+        <v>0.002398580492610387</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>240</v>
+      </c>
+      <c r="B118">
+        <v>7563</v>
+      </c>
+      <c r="C118">
+        <v>1611</v>
+      </c>
+      <c r="D118">
+        <v>-11.17794748286347</v>
+      </c>
+      <c r="E118">
+        <v>11.22799204065259</v>
+      </c>
+      <c r="F118">
+        <v>0.05004455778912231</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>241</v>
+      </c>
+      <c r="B119">
+        <v>4427</v>
+      </c>
+      <c r="C119">
+        <v>7279</v>
+      </c>
+      <c r="D119">
+        <v>-0.1864481075925904</v>
+      </c>
+      <c r="E119">
+        <v>0.1871918651119616</v>
+      </c>
+      <c r="F119">
+        <v>0.0007437575193712216</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>242</v>
+      </c>
+      <c r="B120">
+        <v>4427</v>
+      </c>
+      <c r="C120">
+        <v>8335</v>
+      </c>
+      <c r="D120">
+        <v>-0.1426920697134114</v>
+      </c>
+      <c r="E120">
+        <v>0.1454001000760765</v>
+      </c>
+      <c r="F120">
+        <v>0.002708030362665145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>243</v>
+      </c>
+      <c r="B121">
+        <v>4427</v>
+      </c>
+      <c r="C121">
+        <v>5155</v>
+      </c>
+      <c r="D121">
+        <v>-6.561246040451461</v>
+      </c>
+      <c r="E121">
+        <v>6.564771879780719</v>
+      </c>
+      <c r="F121">
+        <v>0.003525839329257541</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>244</v>
+      </c>
+      <c r="B122">
+        <v>4427</v>
+      </c>
+      <c r="C122">
+        <v>271</v>
+      </c>
+      <c r="D122">
+        <v>-8.727739274855411</v>
+      </c>
+      <c r="E122">
+        <v>8.739090015137236</v>
+      </c>
+      <c r="F122">
+        <v>0.01135074028182637</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123">
+        <v>2449</v>
+      </c>
+      <c r="C123">
+        <v>4427</v>
+      </c>
+      <c r="D123">
+        <v>0.04741529951113101</v>
+      </c>
+      <c r="E123">
+        <v>-0.04720946663391648</v>
+      </c>
+      <c r="F123">
+        <v>0.0002058328772145345</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124">
+        <v>4665</v>
+      </c>
+      <c r="C124">
+        <v>4427</v>
+      </c>
+      <c r="D124">
+        <v>-0.161257857746974</v>
+      </c>
+      <c r="E124">
+        <v>0.1614506539309978</v>
+      </c>
+      <c r="F124">
+        <v>0.0001927961840237974</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125">
+        <v>4495</v>
+      </c>
+      <c r="C125">
+        <v>4427</v>
+      </c>
+      <c r="D125">
+        <v>-6.49548902934519</v>
+      </c>
+      <c r="E125">
+        <v>6.500304758312568</v>
+      </c>
+      <c r="F125">
+        <v>0.004815728967377808</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>248</v>
+      </c>
+      <c r="B126">
+        <v>4427</v>
+      </c>
+      <c r="C126">
+        <v>1611</v>
+      </c>
+      <c r="D126">
+        <v>-0.3968077084432948</v>
+      </c>
+      <c r="E126">
+        <v>0.3979882956977964</v>
+      </c>
+      <c r="F126">
+        <v>0.001180587254501556</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>249</v>
+      </c>
+      <c r="B127">
+        <v>5210</v>
+      </c>
+      <c r="C127">
+        <v>1445</v>
+      </c>
+      <c r="D127">
+        <v>11.86182686378279</v>
+      </c>
+      <c r="E127">
+        <v>-11.85289052699839</v>
+      </c>
+      <c r="F127">
+        <v>0.008936336784405585</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>250</v>
+      </c>
+      <c r="B128">
+        <v>8179</v>
+      </c>
+      <c r="C128">
+        <v>5509</v>
+      </c>
+      <c r="D128">
+        <v>-15.83277136609112</v>
+      </c>
+      <c r="E128">
+        <v>15.83729800801104</v>
+      </c>
+      <c r="F128">
+        <v>0.00452664191992469</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>251</v>
+      </c>
+      <c r="B129">
+        <v>8179</v>
+      </c>
+      <c r="C129">
+        <v>7762</v>
+      </c>
+      <c r="D129">
+        <v>35.60397439628668</v>
+      </c>
+      <c r="E129">
+        <v>-35.59392160790381</v>
+      </c>
+      <c r="F129">
+        <v>0.01005278838286938</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>252</v>
+      </c>
+      <c r="B130">
+        <v>7279</v>
+      </c>
+      <c r="C130">
+        <v>4014</v>
+      </c>
+      <c r="D130">
+        <v>-13.98292677451763</v>
+      </c>
+      <c r="E130">
+        <v>13.98292677451763</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>253</v>
+      </c>
+      <c r="B131">
+        <v>8335</v>
+      </c>
+      <c r="C131">
+        <v>7279</v>
+      </c>
+      <c r="D131">
+        <v>1.793843346879064</v>
+      </c>
+      <c r="E131">
+        <v>-1.713552064981857</v>
+      </c>
+      <c r="F131">
+        <v>0.08029128189720632</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>254</v>
+      </c>
+      <c r="B132">
+        <v>5155</v>
+      </c>
+      <c r="C132">
+        <v>7279</v>
+      </c>
+      <c r="D132">
+        <v>-0.02363752492515692</v>
+      </c>
+      <c r="E132">
+        <v>0.02393567325719395</v>
+      </c>
+      <c r="F132">
+        <v>0.0002981483320370289</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>255</v>
+      </c>
+      <c r="B133">
+        <v>271</v>
+      </c>
+      <c r="C133">
+        <v>7279</v>
+      </c>
+      <c r="D133">
+        <v>-0.02232166355402884</v>
+      </c>
+      <c r="E133">
+        <v>0.02241609073374565</v>
+      </c>
+      <c r="F133">
+        <v>9.442717971680883E-05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>256</v>
+      </c>
+      <c r="B134">
+        <v>2449</v>
+      </c>
+      <c r="C134">
+        <v>7279</v>
+      </c>
+      <c r="D134">
+        <v>-0.3832313547885982</v>
+      </c>
+      <c r="E134">
+        <v>0.3838565578799548</v>
+      </c>
+      <c r="F134">
+        <v>0.0006252030913566839</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>257</v>
+      </c>
+      <c r="B135">
+        <v>4665</v>
+      </c>
+      <c r="C135">
+        <v>7279</v>
+      </c>
+      <c r="D135">
+        <v>-0.3741429862891304</v>
+      </c>
+      <c r="E135">
+        <v>0.3761011561540342</v>
+      </c>
+      <c r="F135">
+        <v>0.001958169864903778</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>258</v>
+      </c>
+      <c r="B136">
+        <v>4495</v>
+      </c>
+      <c r="C136">
+        <v>7279</v>
+      </c>
+      <c r="D136">
+        <v>-0.1966094254247796</v>
+      </c>
+      <c r="E136">
+        <v>0.1975078632002321</v>
+      </c>
+      <c r="F136">
+        <v>0.0008984377754524785</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>259</v>
+      </c>
+      <c r="B137">
+        <v>1611</v>
+      </c>
+      <c r="C137">
+        <v>7279</v>
+      </c>
+      <c r="D137">
+        <v>9.929545620341827</v>
+      </c>
+      <c r="E137">
+        <v>-9.886641237859685</v>
+      </c>
+      <c r="F137">
+        <v>0.04290438248214234</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>260</v>
+      </c>
+      <c r="B138">
+        <v>5509</v>
+      </c>
+      <c r="C138">
+        <v>1579</v>
+      </c>
+      <c r="D138">
+        <v>3.48798560583844</v>
+      </c>
+      <c r="E138">
+        <v>-3.487552193705384</v>
+      </c>
+      <c r="F138">
+        <v>0.0004334121330565321</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>261</v>
+      </c>
+      <c r="B139">
+        <v>8335</v>
+      </c>
+      <c r="C139">
+        <v>1531</v>
+      </c>
+      <c r="D139">
+        <v>1.250588565634506</v>
+      </c>
+      <c r="E139">
+        <v>-1.250588565634506</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>262</v>
+      </c>
+      <c r="B140">
+        <v>5155</v>
+      </c>
+      <c r="C140">
+        <v>8335</v>
+      </c>
+      <c r="D140">
+        <v>-0.04622554384915886</v>
+      </c>
+      <c r="E140">
+        <v>0.0478075668025014</v>
+      </c>
+      <c r="F140">
+        <v>0.001582022953342546</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141">
+        <v>2449</v>
+      </c>
+      <c r="C141">
+        <v>8335</v>
+      </c>
+      <c r="D141">
+        <v>-1.641795495053421</v>
+      </c>
+      <c r="E141">
+        <v>1.663638036119273</v>
+      </c>
+      <c r="F141">
+        <v>0.02184254106585119</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>264</v>
+      </c>
+      <c r="B142">
+        <v>4665</v>
+      </c>
+      <c r="C142">
+        <v>8335</v>
+      </c>
+      <c r="D142">
+        <v>-1.287485263987598</v>
+      </c>
+      <c r="E142">
+        <v>1.302393340938838</v>
+      </c>
+      <c r="F142">
+        <v>0.01490807695123924</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>265</v>
+      </c>
+      <c r="B143">
+        <v>4495</v>
+      </c>
+      <c r="C143">
+        <v>8335</v>
+      </c>
+      <c r="D143">
+        <v>-0.9584193113289557</v>
+      </c>
+      <c r="E143">
+        <v>0.9687451304353941</v>
+      </c>
+      <c r="F143">
+        <v>0.01032581910643832</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>266</v>
+      </c>
+      <c r="B144">
+        <v>7762</v>
+      </c>
+      <c r="C144">
+        <v>2268</v>
+      </c>
+      <c r="D144">
+        <v>-63.32153311251769</v>
+      </c>
+      <c r="E144">
+        <v>63.35297538480017</v>
+      </c>
+      <c r="F144">
+        <v>0.03144227228247809</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>267</v>
+      </c>
+      <c r="B145">
+        <v>5155</v>
+      </c>
+      <c r="C145">
+        <v>271</v>
+      </c>
+      <c r="D145">
+        <v>-0.3556494797844747</v>
+      </c>
+      <c r="E145">
+        <v>0.3599341364458228</v>
+      </c>
+      <c r="F145">
+        <v>0.004284656661348142</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>268</v>
+      </c>
+      <c r="B146">
+        <v>5155</v>
+      </c>
+      <c r="C146">
+        <v>2908</v>
+      </c>
+      <c r="D146">
+        <v>-1.234896264090504</v>
+      </c>
+      <c r="E146">
+        <v>1.252714677087502</v>
+      </c>
+      <c r="F146">
+        <v>0.01781841299699719</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>269</v>
+      </c>
+      <c r="B147">
+        <v>4665</v>
+      </c>
+      <c r="C147">
+        <v>5155</v>
+      </c>
+      <c r="D147">
+        <v>-0.208303410159318</v>
+      </c>
+      <c r="E147">
+        <v>0.2083410592624414</v>
+      </c>
+      <c r="F147">
+        <v>3.764910312346187E-05</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>270</v>
+      </c>
+      <c r="B148">
+        <v>4495</v>
+      </c>
+      <c r="C148">
+        <v>5155</v>
+      </c>
+      <c r="D148">
+        <v>-0.2814821438943239</v>
+      </c>
+      <c r="E148">
+        <v>0.2816630558183831</v>
+      </c>
+      <c r="F148">
+        <v>0.0001809119240592846</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>271</v>
+      </c>
+      <c r="B149">
+        <v>5155</v>
+      </c>
+      <c r="C149">
+        <v>1611</v>
+      </c>
+      <c r="D149">
+        <v>-24.41655589210571</v>
+      </c>
+      <c r="E149">
+        <v>24.46764514716999</v>
+      </c>
+      <c r="F149">
+        <v>0.05108925506428774</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>272</v>
+      </c>
+      <c r="B150">
+        <v>271</v>
+      </c>
+      <c r="C150">
+        <v>2908</v>
+      </c>
+      <c r="D150">
+        <v>0.4809757756549971</v>
+      </c>
+      <c r="E150">
+        <v>-0.4803671826371571</v>
+      </c>
+      <c r="F150">
+        <v>0.0006085930178399875</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>273</v>
+      </c>
+      <c r="B151">
+        <v>4665</v>
+      </c>
+      <c r="C151">
+        <v>271</v>
+      </c>
+      <c r="D151">
+        <v>-0.123212483809943</v>
+      </c>
+      <c r="E151">
+        <v>0.1232280343271745</v>
+      </c>
+      <c r="F151">
+        <v>1.555051723149507E-05</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>274</v>
+      </c>
+      <c r="B152">
+        <v>4495</v>
+      </c>
+      <c r="C152">
+        <v>271</v>
+      </c>
+      <c r="D152">
+        <v>-0.1813113652890821</v>
+      </c>
+      <c r="E152">
+        <v>0.1816271993293625</v>
+      </c>
+      <c r="F152">
+        <v>0.0003158340402804102</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>275</v>
+      </c>
+      <c r="B153">
+        <v>271</v>
+      </c>
+      <c r="C153">
+        <v>1611</v>
+      </c>
+      <c r="D153">
+        <v>-23.30352676477387</v>
+      </c>
+      <c r="E153">
+        <v>23.36046194666092</v>
+      </c>
+      <c r="F153">
+        <v>0.05693518188704116</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>276</v>
+      </c>
+      <c r="B154">
+        <v>1579</v>
+      </c>
+      <c r="C154">
+        <v>5848</v>
+      </c>
+      <c r="D154">
+        <v>0.8836470843283931</v>
+      </c>
+      <c r="E154">
+        <v>-0.8835148268482742</v>
+      </c>
+      <c r="F154">
+        <v>0.0001322574801189066</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>277</v>
+      </c>
+      <c r="B155">
+        <v>7051</v>
+      </c>
+      <c r="C155">
+        <v>8847</v>
+      </c>
+      <c r="D155">
+        <v>-9.054401073825618</v>
+      </c>
+      <c r="E155">
+        <v>9.054704703039842</v>
+      </c>
+      <c r="F155">
+        <v>0.0003036292142252761</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>278</v>
+      </c>
+      <c r="B156">
+        <v>5776</v>
+      </c>
+      <c r="C156">
+        <v>8229</v>
+      </c>
+      <c r="D156">
+        <v>-0.9278864858966627</v>
+      </c>
+      <c r="E156">
+        <v>0.9278864858966627</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>279</v>
+      </c>
+      <c r="B157">
+        <v>317</v>
+      </c>
+      <c r="C157">
+        <v>6233</v>
+      </c>
+      <c r="D157">
+        <v>126.2814430363402</v>
+      </c>
+      <c r="E157">
+        <v>-126.2777314338682</v>
+      </c>
+      <c r="F157">
+        <v>0.003711602472011855</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>280</v>
+      </c>
+      <c r="B158">
+        <v>4665</v>
+      </c>
+      <c r="C158">
+        <v>2449</v>
+      </c>
+      <c r="D158">
+        <v>-2.556719920021265</v>
+      </c>
+      <c r="E158">
+        <v>2.560027367122885</v>
+      </c>
+      <c r="F158">
+        <v>0.003307447101619579</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>281</v>
+      </c>
+      <c r="B159">
+        <v>2449</v>
+      </c>
+      <c r="C159">
+        <v>4495</v>
+      </c>
+      <c r="D159">
+        <v>3.540824559070237</v>
+      </c>
+      <c r="E159">
+        <v>-3.536368097384512</v>
+      </c>
+      <c r="F159">
+        <v>0.004456461685724972</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>282</v>
+      </c>
+      <c r="B160">
+        <v>4665</v>
+      </c>
+      <c r="C160">
+        <v>4495</v>
+      </c>
+      <c r="D160">
+        <v>2.384868734553811</v>
+      </c>
+      <c r="E160">
+        <v>-2.383869062221805</v>
+      </c>
+      <c r="F160">
+        <v>0.0009996723320058326</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>283</v>
+      </c>
+      <c r="B161">
+        <v>1611</v>
+      </c>
+      <c r="C161">
+        <v>8420</v>
+      </c>
+      <c r="D161">
+        <v>19.7772138388116</v>
+      </c>
+      <c r="E161">
+        <v>-19.7772138388116</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>284</v>
+      </c>
+      <c r="B162">
+        <v>7829</v>
+      </c>
+      <c r="C162">
+        <v>1968</v>
+      </c>
+      <c r="D162">
+        <v>-0.1168843944738956</v>
+      </c>
+      <c r="E162">
+        <v>0.1169710706899874</v>
+      </c>
+      <c r="F162">
+        <v>8.667621609181192E-05</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>285</v>
+      </c>
+      <c r="B163">
+        <v>1815</v>
+      </c>
+      <c r="C163">
+        <v>792</v>
+      </c>
+      <c r="D163">
+        <v>-0.04188964249306198</v>
+      </c>
+      <c r="E163">
+        <v>0.04268732376699828</v>
+      </c>
+      <c r="F163">
+        <v>0.0007976812739362985</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>286</v>
+      </c>
+      <c r="B164">
+        <v>7829</v>
+      </c>
+      <c r="C164">
+        <v>6826</v>
+      </c>
+      <c r="D164">
+        <v>2.357419364563796</v>
+      </c>
+      <c r="E164">
+        <v>-2.357372317627252</v>
+      </c>
+      <c r="F164">
+        <v>4.704693654447589E-05</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>287</v>
+      </c>
+      <c r="B165">
+        <v>5210</v>
+      </c>
+      <c r="C165">
+        <v>792</v>
+      </c>
+      <c r="D165">
+        <v>-1.299089703128175</v>
+      </c>
+      <c r="E165">
+        <v>1.301124952138879</v>
+      </c>
+      <c r="F165">
+        <v>0.002035249010704301</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>288</v>
+      </c>
+      <c r="B166">
+        <v>1445</v>
+      </c>
+      <c r="C166">
+        <v>792</v>
+      </c>
+      <c r="D166">
+        <v>-6.7136514721416</v>
+      </c>
+      <c r="E166">
+        <v>6.71522163524862</v>
+      </c>
+      <c r="F166">
+        <v>0.001570163107018907</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>289</v>
+      </c>
+      <c r="B167">
+        <v>5210</v>
+      </c>
+      <c r="C167">
+        <v>7279</v>
+      </c>
+      <c r="D167">
+        <v>0.9186577291619825</v>
+      </c>
+      <c r="E167">
+        <v>-0.9035841793300867</v>
+      </c>
+      <c r="F167">
+        <v>0.01507354983189581</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>290</v>
+      </c>
+      <c r="B168">
+        <v>5210</v>
+      </c>
+      <c r="C168">
+        <v>8335</v>
+      </c>
+      <c r="D168">
+        <v>3.197189707478786</v>
+      </c>
+      <c r="E168">
+        <v>-3.184307296687358</v>
+      </c>
+      <c r="F168">
+        <v>0.01288241079142743</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>291</v>
+      </c>
+      <c r="B169">
+        <v>5210</v>
+      </c>
+      <c r="C169">
+        <v>2449</v>
+      </c>
+      <c r="D169">
+        <v>1.536565838239337</v>
+      </c>
+      <c r="E169">
+        <v>-1.517255839624234</v>
+      </c>
+      <c r="F169">
+        <v>0.0193099986151031</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>292</v>
+      </c>
+      <c r="B170">
+        <v>5210</v>
+      </c>
+      <c r="C170">
+        <v>4665</v>
+      </c>
+      <c r="D170">
+        <v>0.6257215840673305</v>
+      </c>
+      <c r="E170">
+        <v>-0.6104963529556605</v>
+      </c>
+      <c r="F170">
+        <v>0.01522523111166995</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>293</v>
+      </c>
+      <c r="B171">
+        <v>5210</v>
+      </c>
+      <c r="C171">
+        <v>4495</v>
+      </c>
+      <c r="D171">
+        <v>0.4506723806322482</v>
+      </c>
+      <c r="E171">
+        <v>-0.4418923906596788</v>
+      </c>
+      <c r="F171">
+        <v>0.008779989972569451</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>294</v>
+      </c>
+      <c r="B172">
+        <v>1445</v>
+      </c>
+      <c r="C172">
+        <v>7279</v>
+      </c>
+      <c r="D172">
+        <v>0.4240615849013342</v>
+      </c>
+      <c r="E172">
+        <v>-0.4141819368943639</v>
+      </c>
+      <c r="F172">
+        <v>0.009879648006970269</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>295</v>
+      </c>
+      <c r="B173">
+        <v>1445</v>
+      </c>
+      <c r="C173">
+        <v>8335</v>
+      </c>
+      <c r="D173">
+        <v>1.117379709118874</v>
+      </c>
+      <c r="E173">
+        <v>-1.110520594947665</v>
+      </c>
+      <c r="F173">
+        <v>0.006859114171208804</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>296</v>
+      </c>
+      <c r="B174">
+        <v>7829</v>
+      </c>
+      <c r="C174">
+        <v>5776</v>
+      </c>
+      <c r="D174">
+        <v>0.4653498759616738</v>
+      </c>
+      <c r="E174">
+        <v>-0.465296183638502</v>
+      </c>
+      <c r="F174">
+        <v>5.369232317182712E-05</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>297</v>
+      </c>
+      <c r="B175">
+        <v>1445</v>
+      </c>
+      <c r="C175">
+        <v>2449</v>
+      </c>
+      <c r="D175">
+        <v>0.77973548398768</v>
+      </c>
+      <c r="E175">
+        <v>-0.7648260669399797</v>
+      </c>
+      <c r="F175">
+        <v>0.0149094170477003</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>298</v>
+      </c>
+      <c r="B176">
+        <v>1445</v>
+      </c>
+      <c r="C176">
+        <v>4665</v>
+      </c>
+      <c r="D176">
+        <v>0.2782848056158389</v>
+      </c>
+      <c r="E176">
+        <v>-0.2709205652020209</v>
+      </c>
+      <c r="F176">
+        <v>0.007364240413818002</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>299</v>
+      </c>
+      <c r="B177">
+        <v>7637</v>
+      </c>
+      <c r="C177">
+        <v>8581</v>
+      </c>
+      <c r="D177">
+        <v>-5.691718008833735</v>
+      </c>
+      <c r="E177">
+        <v>5.691759052962991</v>
+      </c>
+      <c r="F177">
+        <v>4.10441292550412E-05</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178">
+        <v>5848</v>
+      </c>
+      <c r="C178">
+        <v>7526</v>
+      </c>
+      <c r="D178">
+        <v>0.2827872754423177</v>
+      </c>
+      <c r="E178">
+        <v>-0.2827857650760962</v>
+      </c>
+      <c r="F178">
+        <v>1.510366221544115E-06</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>301</v>
+      </c>
+      <c r="B179">
+        <v>2154</v>
+      </c>
+      <c r="C179">
+        <v>5996</v>
+      </c>
+      <c r="D179">
+        <v>38.09249002791076</v>
+      </c>
+      <c r="E179">
+        <v>-38.09096761767772</v>
+      </c>
+      <c r="F179">
+        <v>0.001522410233034677</v>
       </c>
     </row>
   </sheetData>
@@ -2981,7 +7943,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2989,119 +7951,659 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>303</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>304</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>9024</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>6542</v>
       </c>
       <c r="D2">
-        <v>102.7759528167307</v>
+        <v>-5.061729886147978</v>
       </c>
       <c r="E2">
-        <v>-102.521366472144</v>
+        <v>5.061959013550885</v>
       </c>
       <c r="F2">
-        <v>0.2545863445867047</v>
+        <v>0.0002291274029071755</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>305</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>9024</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>6542</v>
       </c>
       <c r="D3">
-        <v>75.48600449002028</v>
+        <v>-5.234060754623424</v>
       </c>
       <c r="E3">
-        <v>-75.34903148264421</v>
+        <v>5.234724196349244</v>
       </c>
       <c r="F3">
-        <v>0.1369730073760622</v>
+        <v>0.0006634417258205572</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>306</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>6069</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>9192</v>
       </c>
       <c r="D4">
-        <v>79.949018079864</v>
+        <v>-2.475198797957686</v>
       </c>
       <c r="E4">
-        <v>-79.79386416896489</v>
+        <v>2.479281314369904</v>
       </c>
       <c r="F4">
-        <v>0.1551539108991196</v>
+        <v>0.004082516412217546</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>307</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>6069</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>1968</v>
       </c>
       <c r="D5">
-        <v>121.5393515866439</v>
+        <v>-3.267556432554679</v>
       </c>
       <c r="E5">
-        <v>-121.1760275501905</v>
+        <v>3.270572377923805</v>
       </c>
       <c r="F5">
-        <v>0.3633240364533386</v>
+        <v>0.003015945369126</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>8574</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>2299</v>
       </c>
       <c r="D6">
-        <v>126.3196164546818</v>
+        <v>-11.46635092926594</v>
       </c>
       <c r="E6">
-        <v>-125.9370141518932</v>
+        <v>11.47153684171366</v>
       </c>
       <c r="F6">
-        <v>0.3826023027886594</v>
+        <v>0.005185912447717989</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7">
+        <v>8574</v>
+      </c>
+      <c r="C7">
+        <v>5587</v>
+      </c>
+      <c r="D7">
+        <v>-7.964473745888966</v>
+      </c>
+      <c r="E7">
+        <v>7.970953467312531</v>
+      </c>
+      <c r="F7">
+        <v>0.006479721423564844</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8">
+        <v>4929</v>
+      </c>
+      <c r="C8">
+        <v>1815</v>
+      </c>
+      <c r="D8">
+        <v>-12.57198618914065</v>
+      </c>
+      <c r="E8">
+        <v>12.57376596066723</v>
+      </c>
+      <c r="F8">
+        <v>0.001779771526580487</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9">
+        <v>6704</v>
+      </c>
+      <c r="C9">
+        <v>4586</v>
+      </c>
+      <c r="D9">
+        <v>-1.398929652353734</v>
+      </c>
+      <c r="E9">
+        <v>1.40029308275658</v>
+      </c>
+      <c r="F9">
+        <v>0.001363430402846061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10">
+        <v>2441</v>
+      </c>
+      <c r="C10">
+        <v>3506</v>
+      </c>
+      <c r="D10">
+        <v>-1.802065790728395</v>
+      </c>
+      <c r="E10">
+        <v>1.805174096171538</v>
+      </c>
+      <c r="F10">
+        <v>0.003108305443142931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11">
+        <v>1367</v>
+      </c>
+      <c r="C11">
+        <v>6826</v>
+      </c>
+      <c r="D11">
+        <v>-22.09427956063782</v>
+      </c>
+      <c r="E11">
+        <v>22.0983246293586</v>
+      </c>
+      <c r="F11">
+        <v>0.004045068720784362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12">
+        <v>1676</v>
+      </c>
+      <c r="C12">
+        <v>228</v>
+      </c>
+      <c r="D12">
+        <v>-1.042395540641659</v>
+      </c>
+      <c r="E12">
+        <v>1.042669371859213</v>
+      </c>
+      <c r="F12">
+        <v>0.0002738312175542754</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13">
+        <v>659</v>
+      </c>
+      <c r="C13">
+        <v>3279</v>
+      </c>
+      <c r="D13">
+        <v>-38.09930753546011</v>
+      </c>
+      <c r="E13">
+        <v>38.11788759613186</v>
+      </c>
+      <c r="F13">
+        <v>0.01858006067174678</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14">
+        <v>7180</v>
+      </c>
+      <c r="C14">
+        <v>2168</v>
+      </c>
+      <c r="D14">
+        <v>-2.707792215312948</v>
+      </c>
+      <c r="E14">
+        <v>2.708412461575961</v>
+      </c>
+      <c r="F14">
+        <v>0.000620246263013241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>317</v>
+      </c>
+      <c r="B15">
+        <v>6833</v>
+      </c>
+      <c r="C15">
+        <v>8964</v>
+      </c>
+      <c r="D15">
+        <v>-3.881141032143315</v>
+      </c>
+      <c r="E15">
+        <v>3.893371961539675</v>
+      </c>
+      <c r="F15">
+        <v>0.01223092939635975</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16">
+        <v>3659</v>
+      </c>
+      <c r="C16">
+        <v>3242</v>
+      </c>
+      <c r="D16">
+        <v>-118.5540588561873</v>
+      </c>
+      <c r="E16">
+        <v>118.6369159945807</v>
+      </c>
+      <c r="F16">
+        <v>0.0828571383934662</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17">
+        <v>8181</v>
+      </c>
+      <c r="C17">
+        <v>4427</v>
+      </c>
+      <c r="D17">
+        <v>-15.63034782543224</v>
+      </c>
+      <c r="E17">
+        <v>15.63294043436475</v>
+      </c>
+      <c r="F17">
+        <v>0.002592608932514007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>320</v>
+      </c>
+      <c r="B18">
+        <v>9025</v>
+      </c>
+      <c r="C18">
+        <v>7563</v>
+      </c>
+      <c r="D18">
+        <v>-30.63217904481112</v>
+      </c>
+      <c r="E18">
+        <v>30.63766908994547</v>
+      </c>
+      <c r="F18">
+        <v>0.005490045134348698</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19">
+        <v>2267</v>
+      </c>
+      <c r="C19">
+        <v>5210</v>
+      </c>
+      <c r="D19">
+        <v>-49.09144314338705</v>
+      </c>
+      <c r="E19">
+        <v>49.10282322265531</v>
+      </c>
+      <c r="F19">
+        <v>0.01138007926825835</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>322</v>
+      </c>
+      <c r="B20">
+        <v>8179</v>
+      </c>
+      <c r="C20">
+        <v>7279</v>
+      </c>
+      <c r="D20">
+        <v>-23.43533203177424</v>
+      </c>
+      <c r="E20">
+        <v>23.44061418951638</v>
+      </c>
+      <c r="F20">
+        <v>0.005282157742134141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21">
+        <v>5509</v>
+      </c>
+      <c r="C21">
+        <v>8335</v>
+      </c>
+      <c r="D21">
+        <v>-15.32641786073121</v>
+      </c>
+      <c r="E21">
+        <v>15.32808595930418</v>
+      </c>
+      <c r="F21">
+        <v>0.001668098572962795</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B22">
+        <v>5509</v>
+      </c>
+      <c r="C22">
+        <v>1531</v>
+      </c>
+      <c r="D22">
+        <v>-13.28549194153533</v>
+      </c>
+      <c r="E22">
+        <v>13.29171393912369</v>
+      </c>
+      <c r="F22">
+        <v>0.006221997588357064</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>325</v>
+      </c>
+      <c r="B23">
+        <v>7762</v>
+      </c>
+      <c r="C23">
+        <v>5155</v>
+      </c>
+      <c r="D23">
+        <v>-31.0690692935275</v>
+      </c>
+      <c r="E23">
+        <v>31.07895335656749</v>
+      </c>
+      <c r="F23">
+        <v>0.009884063039983237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24">
+        <v>7762</v>
+      </c>
+      <c r="C24">
+        <v>271</v>
+      </c>
+      <c r="D24">
+        <v>-27.13455333706408</v>
+      </c>
+      <c r="E24">
+        <v>27.14422690678266</v>
+      </c>
+      <c r="F24">
+        <v>0.009673569718587904</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25">
+        <v>8329</v>
+      </c>
+      <c r="C25">
+        <v>1445</v>
+      </c>
+      <c r="D25">
+        <v>-25.22502645812693</v>
+      </c>
+      <c r="E25">
+        <v>25.2315452033551</v>
+      </c>
+      <c r="F25">
+        <v>0.006518745228167866</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26">
+        <v>8329</v>
+      </c>
+      <c r="C26">
+        <v>1445</v>
+      </c>
+      <c r="D26">
+        <v>-25.77659339038264</v>
+      </c>
+      <c r="E26">
+        <v>25.78357482563532</v>
+      </c>
+      <c r="F26">
+        <v>0.006981435252689794</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27">
+        <v>2268</v>
+      </c>
+      <c r="C27">
+        <v>2908</v>
+      </c>
+      <c r="D27">
+        <v>-14.22611642431729</v>
+      </c>
+      <c r="E27">
+        <v>14.2272347599507</v>
+      </c>
+      <c r="F27">
+        <v>0.001118335633404355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28">
+        <v>8847</v>
+      </c>
+      <c r="C28">
+        <v>5776</v>
+      </c>
+      <c r="D28">
+        <v>-3.925685244439158</v>
+      </c>
+      <c r="E28">
+        <v>3.926947499243764</v>
+      </c>
+      <c r="F28">
+        <v>0.001262254804606372</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29">
+        <v>8847</v>
+      </c>
+      <c r="C29">
+        <v>8103</v>
+      </c>
+      <c r="D29">
+        <v>-1.238926753015159</v>
+      </c>
+      <c r="E29">
+        <v>1.238969096081975</v>
+      </c>
+      <c r="F29">
+        <v>4.234306681602518E-05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30">
+        <v>317</v>
+      </c>
+      <c r="C30">
+        <v>2449</v>
+      </c>
+      <c r="D30">
+        <v>-25.52951574379693</v>
+      </c>
+      <c r="E30">
+        <v>25.53435202158208</v>
+      </c>
+      <c r="F30">
+        <v>0.004836277785147391</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31">
+        <v>89</v>
+      </c>
+      <c r="C31">
+        <v>4495</v>
+      </c>
+      <c r="D31">
+        <v>-11.46352127956396</v>
+      </c>
+      <c r="E31">
+        <v>11.46626902447009</v>
+      </c>
+      <c r="F31">
+        <v>0.002747744906130001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32">
+        <v>2520</v>
+      </c>
+      <c r="C32">
+        <v>4665</v>
+      </c>
+      <c r="D32">
+        <v>-12.52273663225358</v>
+      </c>
+      <c r="E32">
+        <v>12.52378214064775</v>
+      </c>
+      <c r="F32">
+        <v>0.001045508394167949</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33">
+        <v>5996</v>
+      </c>
+      <c r="C33">
+        <v>8420</v>
+      </c>
+      <c r="D33">
+        <v>-89.08585684651733</v>
+      </c>
+      <c r="E33">
+        <v>89.14009843153364</v>
+      </c>
+      <c r="F33">
+        <v>0.05424158501631249</v>
       </c>
     </row>
   </sheetData>
